--- a/Programacion_conexion_columna_placa_base_AISC.xlsx
+++ b/Programacion_conexion_columna_placa_base_AISC.xlsx
@@ -5,13 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\Proyectos python\StructureLab_HFS_CNT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\byomayusa\Documents\GitHub\StructureLab_HFS_CNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA4F2F8D-EC41-464C-ADDB-8379425613ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638822D9-2A7E-43AE-BE95-3C996B71E505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AB58D246-1225-44B9-9BA8-FD1D7BFD2E17}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DISENO_CONEXION" sheetId="1" r:id="rId1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="625">
   <si>
     <t>CONEXIÓN COLUMNA - PLACA BASE AXIAL + MOMENTO</t>
   </si>
@@ -132,15 +131,9 @@
     <t>Dimensión crítica con el momento.</t>
   </si>
   <si>
-    <t>le borde anclaje</t>
-  </si>
-  <si>
     <t>Distancia borde placa - eje anclaje</t>
   </si>
   <si>
-    <t>Sobresale pedestal</t>
-  </si>
-  <si>
     <t>Pedestal mayor que la placa por borde</t>
   </si>
   <si>
@@ -1906,6 +1899,18 @@
   </si>
   <si>
     <t>C1</t>
+  </si>
+  <si>
+    <t>le borde anclaje X</t>
+  </si>
+  <si>
+    <t>Sobresale pedestal Y</t>
+  </si>
+  <si>
+    <t>le borde anclaje Y</t>
+  </si>
+  <si>
+    <t>Sobresale pedestal X</t>
   </si>
 </sst>
 </file>
@@ -1963,7 +1968,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1995,6 +2000,12 @@
         <fgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2008,7 +2019,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2044,15 +2055,6 @@
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2065,8 +2067,20 @@
     <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2353,8 +2367,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L182"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14"/>
+  <dimension ref="A1:L184"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -2366,29 +2380,29 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22.4" customHeight="1">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:10" ht="22.35" customHeight="1">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1"/>
@@ -2401,26 +2415,26 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="21" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="2" t="s">
@@ -2436,7 +2450,7 @@
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="21" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="4">
@@ -2458,7 +2472,7 @@
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="21" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="4">
@@ -2478,7 +2492,7 @@
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="21" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="4">
@@ -2522,7 +2536,7 @@
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="21" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="10">
@@ -2542,7 +2556,7 @@
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="21" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="4">
@@ -2562,7 +2576,7 @@
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="21" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="10">
@@ -2584,7 +2598,7 @@
       <c r="A13" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="21" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="10">
@@ -2606,8 +2620,8 @@
       <c r="A14" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>31</v>
+      <c r="B14" s="21" t="s">
+        <v>623</v>
       </c>
       <c r="C14" s="12">
         <v>85</v>
@@ -2616,282 +2630,268 @@
         <v>25</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="10">
+      <c r="A15" s="2"/>
+      <c r="B15" s="21" t="s">
+        <v>621</v>
+      </c>
+      <c r="C15" s="12">
         <v>50</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-      <c r="J15">
-        <f>C20/PERFILES!X3</f>
-        <v>0.73786448102190194</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="25">
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>35</v>
+      <c r="B16" s="21" t="s">
+        <v>622</v>
       </c>
       <c r="C16" s="10">
-        <v>430</v>
+        <v>50</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="2" t="s">
-        <v>37</v>
+      <c r="H16" s="2"/>
+      <c r="J16">
+        <f>C22/PERFILES!X3</f>
+        <v>0.73786448102190194</v>
       </c>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>38</v>
+      <c r="A17" s="2"/>
+      <c r="B17" s="21" t="s">
+        <v>624</v>
       </c>
       <c r="C17" s="10">
-        <v>40</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>39</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
-      <c r="K17" s="11">
-        <f>C13-500</f>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+    </row>
+    <row r="18" spans="1:11" ht="25.5">
       <c r="A18" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>40</v>
+      <c r="B18" s="21" t="s">
+        <v>33</v>
       </c>
       <c r="C18" s="10">
-        <v>485</v>
+        <v>430</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>43</v>
+      <c r="B19" s="21" t="s">
+        <v>36</v>
       </c>
       <c r="C19" s="10">
-        <v>2500</v>
+        <v>40</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
-      <c r="K19">
-        <f>K17*0.25</f>
-        <v>75</v>
+      <c r="K19" s="11">
+        <f>C13-500</f>
+        <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>45</v>
+      <c r="B20" s="21" t="s">
+        <v>38</v>
       </c>
       <c r="C20" s="10">
-        <f>C38</f>
-        <v>4814565.73866791</v>
+        <v>485</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K20">
-        <f>(800-500)/2</f>
-        <v>150</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="7"/>
+      <c r="B21" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="10">
+        <v>2500</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="E21" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="K21">
-        <f>K20-80</f>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="25">
+        <f>K19*0.25</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="7"/>
+      <c r="B22" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="10">
+        <f>C40</f>
+        <v>4814565.73866791</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>44</v>
+      </c>
       <c r="E22" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="K22">
-        <f>200/25.4</f>
-        <v>7.8740157480314963</v>
+        <f>(800-500)/2</f>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="4">
-        <v>450</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>25</v>
-      </c>
+      <c r="B23" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="7"/>
       <c r="E23" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="K23">
-        <f>0.45*SQRT(200000/345)</f>
-        <v>10.834726777719228</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+        <f>K22-80</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="25.5">
       <c r="A24" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="4">
-        <v>130</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>25</v>
-      </c>
+      <c r="B24" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="7"/>
       <c r="E24" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
+      <c r="H24" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K24">
+        <f>200/25.4</f>
+        <v>7.8740157480314963</v>
+      </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>60</v>
+      <c r="B25" s="21" t="s">
+        <v>54</v>
       </c>
       <c r="C25" s="4">
-        <v>50.8</v>
+        <v>450</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-      <c r="H25" s="2" t="s">
-        <v>62</v>
+      <c r="H25" s="2"/>
+      <c r="K25">
+        <f>0.45*SQRT(200000/345)</f>
+        <v>10.834726777719228</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>63</v>
+      <c r="B26" s="21" t="s">
+        <v>56</v>
       </c>
       <c r="C26" s="4">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -2901,158 +2901,158 @@
       <c r="A27" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>65</v>
+      <c r="B27" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="C27" s="4">
-        <v>15.875</v>
+        <v>50.8</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>68</v>
+      <c r="B28" s="21" t="s">
+        <v>61</v>
       </c>
       <c r="C28" s="4">
-        <v>6.35</v>
+        <v>90</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
-      <c r="H28" s="2" t="s">
-        <v>70</v>
-      </c>
+      <c r="H28" s="2"/>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>71</v>
+      <c r="B29" s="21" t="s">
+        <v>63</v>
       </c>
       <c r="C29" s="4">
-        <v>90</v>
+        <v>15.875</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
+      <c r="H29" s="2" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>73</v>
+      <c r="B30" s="21" t="s">
+        <v>66</v>
       </c>
       <c r="C30" s="4">
-        <v>22.225000000000001</v>
+        <v>6.35</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="17.649999999999999" customHeight="1">
-      <c r="A31" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="4">
+        <v>90</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" s="5">
+        <v>3</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="4">
+        <v>22.225000000000001</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="17.649999999999999" customHeight="1">
+      <c r="A33" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="17"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" s="5">
         <f>IFERROR(INDEX(PERFILES!$D:$D,MATCH($C$5,PERFILES!$B:$B,0)),"")</f>
         <v>500</v>
       </c>
-      <c r="D32" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" s="5">
-        <f>IFERROR(INDEX(PERFILES!$F:$F,MATCH($C$5,PERFILES!$B:$B,0)),"")</f>
-        <v>300</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" s="5">
-        <f>IFERROR(INDEX(PERFILES!$E:$E,MATCH($C$5,PERFILES!$B:$B,0)),"")</f>
-        <v>14.5</v>
-      </c>
       <c r="D34" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -3060,20 +3060,20 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>78</v>
       </c>
       <c r="C35" s="5">
-        <f>IFERROR(INDEX(PERFILES!$G:$G,MATCH($C$5,PERFILES!$B:$B,0)),"")</f>
-        <v>28</v>
+        <f>IFERROR(INDEX(PERFILES!$F:$F,MATCH($C$5,PERFILES!$B:$B,0)),"")</f>
+        <v>300</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -3081,20 +3081,20 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>79</v>
       </c>
       <c r="C36" s="5">
-        <f>IFERROR(INDEX(PERFILES!$I:$I,MATCH($C$5,PERFILES!$B:$B,0)),"")</f>
-        <v>55</v>
+        <f>IFERROR(INDEX(PERFILES!$E:$E,MATCH($C$5,PERFILES!$B:$B,0)),"")</f>
+        <v>14.5</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -3102,20 +3102,20 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>84</v>
+        <v>75</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>80</v>
       </c>
       <c r="C37" s="5">
-        <f>IFERROR(INDEX(PERFILES!$J:$J,MATCH($C$5,PERFILES!$B:$B,0)),"")</f>
-        <v>34.25</v>
+        <f>IFERROR(INDEX(PERFILES!$G:$G,MATCH($C$5,PERFILES!$B:$B,0)),"")</f>
+        <v>28</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -3123,20 +3123,20 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="5">
+        <f>IFERROR(INDEX(PERFILES!$I:$I,MATCH($C$5,PERFILES!$B:$B,0)),"")</f>
+        <v>55</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C38" s="5">
-        <f>IFERROR(INDEX(PERFILES!$X:$X,MATCH($C$5,PERFILES!$B:$B,0)),"")</f>
-        <v>4814565.73866791</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -3144,20 +3144,20 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>87</v>
+        <v>75</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>82</v>
       </c>
       <c r="C39" s="5">
-        <f>($C$13-0.95*$C$32)/2</f>
-        <v>162.5</v>
+        <f>IFERROR(INDEX(PERFILES!$J:$J,MATCH($C$5,PERFILES!$B:$B,0)),"")</f>
+        <v>34.25</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -3165,20 +3165,20 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>89</v>
+        <v>75</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>83</v>
       </c>
       <c r="C40" s="5">
-        <f>($C$12-0.8*$C$33)/2</f>
-        <v>230</v>
+        <f>IFERROR(INDEX(PERFILES!$X:$X,MATCH($C$5,PERFILES!$B:$B,0)),"")</f>
+        <v>4814565.73866791</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -3186,20 +3186,20 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>85</v>
       </c>
       <c r="C41" s="5">
-        <f>IF($C$21="Sí",$C$39,MAX($C$39,$C$40))</f>
+        <f>($C$13-0.95*$C$34)/2</f>
         <v>162.5</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -3207,183 +3207,185 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>87</v>
       </c>
       <c r="C42" s="5">
-        <f>CEILING($C$32+150,50)</f>
-        <v>650</v>
+        <f>($C$12-0.8*$C$35)/2</f>
+        <v>230</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="2" t="s">
-        <v>95</v>
-      </c>
+      <c r="H42" s="2"/>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>89</v>
       </c>
       <c r="C43" s="5">
-        <f>CEILING($C$33+150,50)</f>
-        <v>450</v>
+        <f>IF($C$23="Sí",$C$41,MAX($C$41,$C$42))</f>
+        <v>162.5</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="17.649999999999999" customHeight="1">
-      <c r="A44" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
+      <c r="H43" s="2"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" s="5">
+        <f>CEILING($C$34+150,50)</f>
+        <v>650</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45" s="4">
-        <v>1212.009</v>
+        <v>84</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" s="5">
+        <f>CEILING($C$35+150,50)</f>
+        <v>450</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>622</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C46" s="4">
-        <v>1609.37</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
+      <c r="H45" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="17.649999999999999" customHeight="1">
+      <c r="A46" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" s="17"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="4">
+        <v>1212.009</v>
+      </c>
+      <c r="D47" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C47" s="4">
-        <v>712.03</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>101</v>
-      </c>
       <c r="E47" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>101</v>
       </c>
       <c r="C48" s="4">
-        <v>1101.0712000000001</v>
+        <v>1609.37</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F48" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>620</v>
+      </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C49" s="4">
+        <v>712.03</v>
+      </c>
+      <c r="D49" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C49" s="4">
-        <v>1687.39</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>104</v>
-      </c>
       <c r="E49" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F49" s="2"/>
+        <v>105</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>620</v>
+      </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C50" s="4">
+        <v>1101.0712000000001</v>
+      </c>
+      <c r="D50" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C50" s="4">
-        <v>847.64</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>101</v>
-      </c>
       <c r="E50" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -3391,20 +3393,19 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C51" s="5">
-        <f>1.1*$C$7*$C$6*$C$38/1000000</f>
-        <v>2009.8404676069192</v>
+        <v>97</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C51" s="4">
+        <v>1687.39</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -3412,20 +3413,19 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C52" s="5">
-        <f>MIN($C$46,$C$51)</f>
-        <v>1609.37</v>
+        <v>97</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C52" s="4">
+        <v>847.64</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -3433,20 +3433,20 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53" s="5">
+        <f>1.1*$C$7*$C$6*$C$40/1000000</f>
+        <v>2009.8404676069192</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C53" s="5">
-        <f>MIN($C$49,$C$51)</f>
-        <v>1687.39</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -3454,20 +3454,20 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>121</v>
+        <v>112</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>115</v>
       </c>
       <c r="C54" s="5">
-        <f>2*$C$7*$C$6*$C$20/(1000*$C$19)</f>
-        <v>1461.7021582595778</v>
+        <f>MIN($C$48,$C$53)</f>
+        <v>1609.37</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -3475,20 +3475,20 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>123</v>
+        <v>112</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>117</v>
       </c>
       <c r="C55" s="5">
-        <f>0.7*$C$6*$C$20/(1000*$C$19)</f>
-        <v>465.08705035532006</v>
+        <f>MIN($C$51,$C$53)</f>
+        <v>1687.39</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -3496,95 +3496,95 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>125</v>
+        <v>112</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>119</v>
       </c>
       <c r="C56" s="5">
-        <f>MAX(MIN($C$50,$C$54),$C$55)</f>
-        <v>847.64</v>
+        <f>2*$C$7*$C$6*$C$22/(1000*$C$21)</f>
+        <v>1461.7021582595778</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8" ht="17.649999999999999" customHeight="1">
-      <c r="A57" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
+    <row r="57" spans="1:8">
+      <c r="A57" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="C57" s="5">
+        <f>0.7*$C$6*$C$22/(1000*$C$21)</f>
+        <v>465.08705035532006</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>129</v>
+        <v>112</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>123</v>
       </c>
       <c r="C58" s="5">
-        <f>$C$52/$C$45*1000</f>
-        <v>1327.8531760077688</v>
+        <f>MAX(MIN($C$52,$C$56),$C$57)</f>
+        <v>847.64</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
     </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C59" s="5">
-        <f>$C$11*0.85*$C$10*$C$12</f>
-        <v>10829</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
+    <row r="59" spans="1:8" ht="17.649999999999999" customHeight="1">
+      <c r="A59" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="B59" s="17"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="17"/>
+      <c r="H59" s="17"/>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>127</v>
       </c>
       <c r="C60" s="5">
-        <f>$C$13/2-($C$45*1000)/(2*$C$59)</f>
-        <v>344.03873857235203</v>
+        <f>$C$54/$C$47*1000</f>
+        <v>1327.8531760077688</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
@@ -3592,18 +3592,20 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C61" s="5" t="str">
-        <f>IF($C$58&lt;=$C$60,"Momento pequeño","Momento grande")</f>
-        <v>Momento grande</v>
-      </c>
-      <c r="D61" s="7"/>
+        <v>129</v>
+      </c>
+      <c r="B61" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="C61" s="5">
+        <f>$C$11*0.85*$C$10*$C$12</f>
+        <v>10829</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>131</v>
+      </c>
       <c r="E61" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
@@ -3611,20 +3613,20 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
+      </c>
+      <c r="B62" s="21" t="s">
+        <v>133</v>
       </c>
       <c r="C62" s="5">
-        <f>IF($C$61="Momento pequeño",$C$13-2*$C$58,0)</f>
-        <v>0</v>
+        <f>$C$13/2-($C$47*1000)/(2*$C$61)</f>
+        <v>344.03873857235203</v>
       </c>
       <c r="D62" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -3632,20 +3634,18 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C63" s="5">
-        <f>IF($C$62&gt;0,$C$45*1000/$C$62,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>133</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="C63" s="5" t="str">
+        <f>IF($C$60&lt;=$C$62,"Momento pequeño","Momento grande")</f>
+        <v>Momento grande</v>
+      </c>
+      <c r="D63" s="7"/>
       <c r="E63" s="2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -3653,20 +3653,20 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C64" s="5">
-        <f>IF($C$62&gt;0,$C$45*1000/($C$12*$C$62),0)</f>
+        <f>IF($C$63="Momento pequeño",$C$13-2*$C$60,0)</f>
         <v>0</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -3674,114 +3674,114 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="2" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C65" s="5">
-        <f>IF(AND($C$61="Momento pequeño",$C$62&gt;=$C$41),1.49*$C$41*SQRT($C$64/$C$8),0)</f>
+        <f>IF($C$64&gt;0,$C$47*1000/$C$64,0)</f>
         <v>0</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
     </row>
-    <row r="66" spans="1:11" ht="26">
+    <row r="66" spans="1:11">
       <c r="A66" s="2" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C66" s="5" t="str">
-        <f>IF($C$61="Momento pequeño","CUMPLE MÉTODO","REVISAR COMO MOMENTO GRANDE")</f>
-        <v>REVISAR COMO MOMENTO GRANDE</v>
-      </c>
-      <c r="D66" s="7"/>
+        <v>142</v>
+      </c>
+      <c r="C66" s="5">
+        <f>IF($C$64&gt;0,$C$47*1000/($C$12*$C$64),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="E66" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
     </row>
-    <row r="67" spans="1:11" ht="17.649999999999999" customHeight="1">
-      <c r="A67" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="B67" s="13"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="15"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
-    </row>
-    <row r="68" spans="1:11">
+    <row r="67" spans="1:11">
+      <c r="A67" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C67" s="5">
+        <f>IF(AND($C$63="Momento pequeño",$C$64&gt;=$C$43),1.49*$C$43*SQRT($C$66/$C$8),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+    </row>
+    <row r="68" spans="1:11" ht="25.5">
       <c r="A68" s="2" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C68" s="5">
-        <f>$C$53/$C$48*1000</f>
-        <v>1532.4985341547394</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>25</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="C68" s="5" t="str">
+        <f>IF($C$63="Momento pequeño","CUMPLE MÉTODO","REVISAR COMO MOMENTO GRANDE")</f>
+        <v>REVISAR COMO MOMENTO GRANDE</v>
+      </c>
+      <c r="D68" s="7"/>
       <c r="E68" s="2" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
     </row>
-    <row r="69" spans="1:11">
-      <c r="A69" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C69" s="5">
-        <f>$C$59</f>
-        <v>10829</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
+    <row r="69" spans="1:11" ht="17.649999999999999" customHeight="1">
+      <c r="A69" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="B69" s="17"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="17"/>
+      <c r="F69" s="17"/>
+      <c r="G69" s="17"/>
+      <c r="H69" s="17"/>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>155</v>
+        <v>126</v>
+      </c>
+      <c r="B70" s="21" t="s">
+        <v>151</v>
       </c>
       <c r="C70" s="5">
-        <f>$C$13/2-($C$48*1000)/(2*$C$69)</f>
-        <v>349.16099362822052</v>
+        <f>$C$55/$C$50*1000</f>
+        <v>1532.4985341547394</v>
       </c>
       <c r="D70" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -3789,18 +3789,20 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C71" s="5" t="str">
-        <f>IF($C$68&gt;$C$70,"Momento grande","Momento pequeño")</f>
-        <v>Momento grande</v>
-      </c>
-      <c r="D71" s="7"/>
+        <v>129</v>
+      </c>
+      <c r="B71" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C71" s="5">
+        <f>$C$61</f>
+        <v>10829</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>131</v>
+      </c>
       <c r="E71" s="2" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -3808,20 +3810,20 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>158</v>
+        <v>126</v>
+      </c>
+      <c r="B72" s="21" t="s">
+        <v>153</v>
       </c>
       <c r="C72" s="5">
-        <f>$C$13/2-$C$14</f>
-        <v>315</v>
+        <f>$C$13/2-($C$50*1000)/(2*$C$71)</f>
+        <v>349.16099362822052</v>
       </c>
       <c r="D72" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -3829,20 +3831,18 @@
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C73" s="5">
-        <f>($C$72+$C$13/2)^2</f>
-        <v>511225</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>162</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="B73" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="C73" s="5" t="str">
+        <f>IF($C$70&gt;$C$72,"Momento grande","Momento pequeño")</f>
+        <v>Momento grande</v>
+      </c>
+      <c r="D73" s="7"/>
       <c r="E73" s="2" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -3850,39 +3850,41 @@
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>164</v>
+        <v>84</v>
+      </c>
+      <c r="B74" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="C74" s="5">
-        <f>2*$C$48*1000*($C$68+$C$72)/$C$69</f>
-        <v>375699.95899898425</v>
+        <f>$C$13/2-$C$14</f>
+        <v>315</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>162</v>
+        <v>25</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
     </row>
-    <row r="75" spans="1:11" ht="25.5" customHeight="1">
+    <row r="75" spans="1:11">
       <c r="A75" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B75" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C75" s="5">
+        <f>($C$74+$C$13/2)^2</f>
+        <v>511225</v>
+      </c>
+      <c r="D75" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C75" s="5" t="str">
-        <f>IF($C$73&gt;=$C$74,"CUMPLE","NO CUMPLE - AUMENTAR PLACA")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="D75" s="7"/>
       <c r="E75" s="2" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -3890,156 +3892,153 @@
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>168</v>
+        <v>158</v>
+      </c>
+      <c r="B76" s="21" t="s">
+        <v>162</v>
       </c>
       <c r="C76" s="5">
-        <f>IF($C$75="CUMPLE",($C$72+$C$13/2)-SQRT(($C$72+$C$13/2)^2-2*$C$48*1000*($C$68+$C$72)/$C$69),0)</f>
-        <v>346.86274162886508</v>
+        <f>2*$C$50*1000*($C$70+$C$74)/$C$71</f>
+        <v>375699.95899898425</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>25</v>
+        <v>160</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" ht="25.5" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C77" s="5">
-        <f>IF($C$75="CUMPLE",($C$72+$C$13/2)+SQRT(($C$72+$C$13/2)^2-2*$C$48*1000*($C$68+$C$72)/$C$69),0)</f>
-        <v>1083.137258371135</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>25</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="B77" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="C77" s="5" t="str">
+        <f>IF($C$75&gt;=$C$76,"CUMPLE","NO CUMPLE - AUMENTAR PLACA")</f>
+        <v>CUMPLE</v>
+      </c>
+      <c r="D77" s="7"/>
       <c r="E77" s="2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
-      <c r="H77" s="2" t="s">
-        <v>172</v>
-      </c>
+      <c r="H77" s="2"/>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="2" t="s">
-        <v>173</v>
+        <v>129</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C78" s="5">
-        <f>IF($C$71="Momento grande",$C$69*$C$76/1000-$C$48,0)</f>
-        <v>2655.1054290989796</v>
+        <f>IF($C$77="CUMPLE",($C$74+$C$13/2)-SQRT(($C$74+$C$13/2)^2-2*$C$50*1000*($C$70+$C$74)/$C$71),0)</f>
+        <v>346.86274162886508</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
-      <c r="K78">
-        <f>160*2+500</f>
-        <v>820</v>
-      </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="2" t="s">
-        <v>176</v>
+        <v>129</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C79" s="5">
-        <f>$C$11*0.85*$C$10</f>
-        <v>15.469999999999999</v>
+        <f>IF($C$77="CUMPLE",($C$74+$C$13/2)+SQRT(($C$74+$C$13/2)^2-2*$C$50*1000*($C$70+$C$74)/$C$71),0)</f>
+        <v>1083.137258371135</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
+      <c r="G79" s="2">
+        <f>IF($C$73="Momento grande",$C$71*$C$62/1000-$C$50,0)</f>
+        <v>2624.5243</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="2" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C80" s="5">
-        <f>IF($C$76&gt;=$C$41,1.49*$C$41*SQRT($C$79/$C$8),0)</f>
-        <v>51.271407878577406</v>
+        <f>IF($C$73="Momento grande",$C$71*$C$78/1000-$C$50,0)</f>
+        <v>2655.1054290989796</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
+      <c r="K80">
+        <f>160*2+500</f>
+        <v>820</v>
+      </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" s="2" t="s">
-        <v>86</v>
+        <v>174</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C81" s="5">
-        <f>$C$72-($C$32-$C$35)/2</f>
-        <v>79</v>
+        <f>$C$11*0.85*$C$10</f>
+        <v>15.469999999999999</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
-      <c r="L81">
-        <f>800-500-80*2</f>
-        <v>140</v>
-      </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" s="2" t="s">
-        <v>183</v>
+        <v>144</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C82" s="5">
-        <f>$C$78*$C$81/1000</f>
-        <v>209.7533288988194</v>
+        <f>IF($C$78&gt;=$C$43,1.49*$C$43*SQRT($C$81/$C$8),0)</f>
+        <v>51.271407878577406</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -4047,41 +4046,45 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" s="2" t="s">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C83" s="5">
-        <f>IF($C$78&gt;0,2.11*SQRT($C$78*1000*$C$81/($C$12*$C$8)),0)</f>
-        <v>62.183951901438938</v>
+        <f>$C$74-($C$34-$C$37)/2</f>
+        <v>79</v>
       </c>
       <c r="D83" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
+      <c r="L83">
+        <f>800-500-80*2</f>
+        <v>140</v>
+      </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" s="2" t="s">
-        <v>146</v>
+        <v>181</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C84" s="5">
-        <f>MAX($C$65,$C$80,$C$83)</f>
-        <v>62.183951901438938</v>
+        <f>$C$80*$C$83/1000</f>
+        <v>209.7533288988194</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
@@ -4089,19 +4092,20 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85" s="2" t="s">
-        <v>3</v>
+        <v>144</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C85" s="4">
-        <v>63.5</v>
+        <v>184</v>
+      </c>
+      <c r="C85" s="5">
+        <f>IF($C$80&gt;0,2.11*SQRT($C$80*1000*$C$83/($C$12*$C$8)),0)</f>
+        <v>62.183951901438938</v>
       </c>
       <c r="D85" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
@@ -4109,92 +4113,91 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C86" s="5" t="str">
-        <f>IF($C$85&gt;=$C$84,"CUMPLE","NO CUMPLE")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="D86" s="7"/>
+        <v>186</v>
+      </c>
+      <c r="C86" s="5">
+        <f>MAX($C$67,$C$82,$C$85)</f>
+        <v>62.183951901438938</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="E86" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
     </row>
-    <row r="87" spans="1:12" ht="17.649999999999999" customHeight="1">
-      <c r="A87" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="B87" s="13"/>
-      <c r="C87" s="14"/>
-      <c r="D87" s="15"/>
-      <c r="E87" s="13"/>
-      <c r="F87" s="13"/>
-      <c r="G87" s="13"/>
-      <c r="H87" s="13"/>
+    <row r="87" spans="1:12">
+      <c r="A87" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="C87" s="4">
+        <v>63.5</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" s="2" t="s">
-        <v>3</v>
+        <v>147</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C88" s="4">
-        <v>31.75</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>25</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="C88" s="5" t="str">
+        <f>IF($C$87&gt;=$C$86,"CUMPLE","NO CUMPLE")</f>
+        <v>CUMPLE</v>
+      </c>
+      <c r="D88" s="7"/>
       <c r="E88" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
     </row>
-    <row r="89" spans="1:12">
-      <c r="A89" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C89" s="5">
-        <f>$C$88/25.4</f>
-        <v>1.25</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
+    <row r="89" spans="1:12" ht="17.649999999999999" customHeight="1">
+      <c r="A89" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="B89" s="17"/>
+      <c r="C89" s="18"/>
+      <c r="D89" s="19"/>
+      <c r="E89" s="17"/>
+      <c r="F89" s="17"/>
+      <c r="G89" s="17"/>
+      <c r="H89" s="17"/>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C90" s="5">
-        <f>VLOOKUP($C$88,CATALOGOS!$A$2:$G$10,4,FALSE)</f>
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="B90" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="C90" s="4">
+        <v>31.75</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>202</v>
+        <v>25</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
@@ -4202,19 +4205,20 @@
     </row>
     <row r="91" spans="1:12">
       <c r="A91" s="2" t="s">
-        <v>3</v>
+        <v>195</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C91" s="4">
-        <v>840</v>
+        <v>196</v>
+      </c>
+      <c r="C91" s="5">
+        <f>$C$90/25.4</f>
+        <v>1.25</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>9</v>
+        <v>197</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
@@ -4222,19 +4226,20 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" s="2" t="s">
-        <v>3</v>
+        <v>195</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C92" s="4">
-        <v>0.75</v>
+        <v>199</v>
+      </c>
+      <c r="C92" s="5">
+        <f>VLOOKUP($C$90,CATALOGOS!$A$2:$G$10,4,FALSE)</f>
+        <v>7</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
@@ -4244,17 +4249,17 @@
       <c r="A93" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>208</v>
+      <c r="B93" s="21" t="s">
+        <v>202</v>
       </c>
       <c r="C93" s="4">
-        <v>7</v>
+        <v>840</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>209</v>
+        <v>9</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -4265,16 +4270,16 @@
         <v>3</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C94" s="4">
-        <v>14</v>
+        <v>0.75</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>209</v>
+        <v>13</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
@@ -4282,20 +4287,19 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C95" s="5">
-        <f>SQRT(4*$C$78*1000/($C$92*0.75*$C$91*$C$93*PI()))</f>
-        <v>31.970248961740815</v>
+        <v>3</v>
+      </c>
+      <c r="B95" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="C95" s="4">
+        <v>7</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -4303,20 +4307,19 @@
     </row>
     <row r="96" spans="1:12">
       <c r="A96" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C96" s="5">
-        <f>PI()/4*($C$89-0.9743/$C$90)^2*25.4^2</f>
-        <v>625.23060332275122</v>
+        <v>3</v>
+      </c>
+      <c r="B96" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="C96" s="4">
+        <v>14</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>162</v>
+        <v>207</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
@@ -4324,20 +4327,20 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C97" s="5">
-        <f>$C$92*$C$93*$C$96*$C$91/1000</f>
-        <v>2757.2669606533332</v>
+        <f>SQRT(4*$C$80*1000/($C$94*0.75*$C$93*$C$95*PI()))</f>
+        <v>31.970248961740815</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
@@ -4345,93 +4348,93 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="2" t="s">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="C98" s="5" t="str">
-        <f>IF($C$97&gt;=$C$78,"CUMPLE","NO CUMPLE")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="D98" s="7"/>
+        <v>213</v>
+      </c>
+      <c r="C98" s="5">
+        <f>PI()/4*($C$91-0.9743/$C$92)^2*25.4^2</f>
+        <v>625.23060332275122</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>160</v>
+      </c>
       <c r="E98" s="2" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
     </row>
-    <row r="99" spans="1:8" ht="17.649999999999999" customHeight="1">
-      <c r="A99" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="B99" s="13"/>
-      <c r="C99" s="14"/>
-      <c r="D99" s="15"/>
-      <c r="E99" s="13"/>
-      <c r="F99" s="13"/>
-      <c r="G99" s="13"/>
-      <c r="H99" s="13"/>
+    <row r="99" spans="1:8">
+      <c r="A99" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C99" s="5">
+        <f>$C$94*$C$95*$C$98*$C$93/1000</f>
+        <v>2757.2669606533332</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="2" t="s">
-        <v>222</v>
+        <v>147</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C100" s="5">
-        <f>$C$13+2*$C$15</f>
-        <v>900</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>25</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="C100" s="5" t="str">
+        <f>IF($C$99&gt;=$C$80,"CUMPLE","NO CUMPLE")</f>
+        <v>CUMPLE</v>
+      </c>
+      <c r="D100" s="7"/>
       <c r="E100" s="2" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
     </row>
-    <row r="101" spans="1:8">
-      <c r="A101" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C101" s="5">
-        <f>$C$12+2*$C$15</f>
-        <v>800</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2"/>
+    <row r="101" spans="1:8" ht="17.649999999999999" customHeight="1">
+      <c r="A101" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="B101" s="17"/>
+      <c r="C101" s="18"/>
+      <c r="D101" s="19"/>
+      <c r="E101" s="17"/>
+      <c r="F101" s="17"/>
+      <c r="G101" s="17"/>
+      <c r="H101" s="17"/>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
+      </c>
+      <c r="B102" s="21" t="s">
+        <v>221</v>
       </c>
       <c r="C102" s="5">
-        <f>$C$14+$C$15</f>
-        <v>135</v>
+        <f>$C$13+2*$C$16</f>
+        <v>900</v>
       </c>
       <c r="D102" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -4439,20 +4442,20 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>229</v>
+        <v>220</v>
+      </c>
+      <c r="B103" s="21" t="s">
+        <v>223</v>
       </c>
       <c r="C103" s="5">
-        <f>1.5*$C$16</f>
-        <v>645</v>
+        <f>$C$12+2*$C$17</f>
+        <v>850</v>
       </c>
       <c r="D103" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
@@ -4460,20 +4463,20 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C104" s="5">
-        <f>MAX(($C$103-$C$102)/2,0)</f>
-        <v>255</v>
+        <f>$C$15+$C$16</f>
+        <v>100</v>
       </c>
       <c r="D104" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
@@ -4481,20 +4484,20 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="2" t="s">
-        <v>233</v>
+        <v>195</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C105" s="5">
-        <f>($C$102+$C$103)*$C$101</f>
-        <v>624000</v>
+        <f>1.5*$C$18</f>
+        <v>645</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>162</v>
+        <v>25</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
@@ -4502,20 +4505,20 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="2" t="s">
-        <v>233</v>
+        <v>195</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="C106" s="5">
-        <f>9*$C$16^2</f>
-        <v>1664100</v>
+        <f>MAX(($C$105-$C$104)/2,0)</f>
+        <v>272.5</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>162</v>
+        <v>25</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
@@ -4523,20 +4526,20 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="2" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C107" s="5">
-        <f>1/(1+2*$C$104/(3*$C$16))</f>
-        <v>0.71666666666666667</v>
+        <f>($C$104+$C$105)*$C$103</f>
+        <v>633250</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -4544,20 +4547,20 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="2" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C108" s="5">
-        <f>IF($C$102&gt;=$C$103,1,0.7+0.3*$C$102/$C$103)</f>
-        <v>0.76279069767441854</v>
+        <f>9*$C$18^2</f>
+        <v>1664100</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -4565,54 +4568,52 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="2" t="s">
-        <v>3</v>
+        <v>236</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C109" s="4">
-        <v>1</v>
+        <v>237</v>
+      </c>
+      <c r="C109" s="5">
+        <f>1/(1+2*$C$106/(3*$C$18))</f>
+        <v>0.70299727520435973</v>
       </c>
       <c r="D109" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
-      <c r="H109" s="2" t="s">
-        <v>245</v>
-      </c>
+      <c r="H109" s="2"/>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="2" t="s">
-        <v>3</v>
+        <v>236</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C110" s="4">
-        <v>1</v>
+        <v>239</v>
+      </c>
+      <c r="C110" s="5">
+        <f>IF($C$104&gt;=$C$105,1,0.7+0.3*$C$104/$C$105)</f>
+        <v>0.74651162790697667</v>
       </c>
       <c r="D110" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
-      <c r="H110" s="2" t="s">
-        <v>248</v>
-      </c>
+      <c r="H110" s="2"/>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C111" s="4">
         <v>1</v>
@@ -4621,48 +4622,51 @@
         <v>13</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
-      <c r="H111" s="2"/>
+      <c r="H111" s="2" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C112" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D112" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
-      <c r="H112" s="2"/>
+      <c r="H112" s="2" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="113" spans="1:11">
       <c r="A113" s="2" t="s">
-        <v>253</v>
+        <v>3</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C113" s="5">
-        <f>$C$112*$C$111*SQRT($C$10)*$C$16^1.5/1000</f>
-        <v>471.82581531747456</v>
+        <v>247</v>
+      </c>
+      <c r="C113" s="4">
+        <v>1</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
@@ -4670,20 +4674,19 @@
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="2" t="s">
-        <v>253</v>
+        <v>3</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C114" s="5">
-        <f>$C$105/$C$106*$C$107*$C$108*$C$109*$C$110*$C$113</f>
-        <v>96.718479731444575</v>
+        <v>249</v>
+      </c>
+      <c r="C114" s="4">
+        <v>10</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
@@ -4691,101 +4694,105 @@
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C115" s="5">
+        <f>$C$114*$C$113*SQRT($C$10)*$C$18^1.5/1000</f>
+        <v>471.82581531747456</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E115" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C115" s="5">
-        <f>$C$92*$C$114</f>
-        <v>72.538859798583431</v>
-      </c>
-      <c r="D115" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
     </row>
-    <row r="116" spans="1:11" ht="39">
+    <row r="116" spans="1:11">
       <c r="A116" s="2" t="s">
-        <v>149</v>
+        <v>251</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C116" s="5" t="str">
-        <f>IF($C$115&gt;=$C$78,"CUMPLE","NO CUMPLE - USAR REFUERZO SUPLEMENTARIO")</f>
-        <v>NO CUMPLE - USAR REFUERZO SUPLEMENTARIO</v>
-      </c>
-      <c r="D116" s="7"/>
+        <v>254</v>
+      </c>
+      <c r="C116" s="5">
+        <f>$C$107/$C$108*$C$109*$C$110*$C$111*$C$112*$C$115</f>
+        <v>94.22533614260189</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>99</v>
+      </c>
       <c r="E116" s="2" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
-      <c r="K116">
-        <f>(750-50-50-12.7*4-7*25.4)/13</f>
-        <v>32.415384615384625</v>
-      </c>
     </row>
     <row r="117" spans="1:11">
       <c r="A117" s="2" t="s">
-        <v>3</v>
+        <v>251</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C117" s="4">
-        <v>420</v>
+        <v>256</v>
+      </c>
+      <c r="C117" s="5">
+        <f>$C$94*$C$116</f>
+        <v>70.66900210695141</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" ht="38.25">
       <c r="A118" s="2" t="s">
-        <v>3</v>
+        <v>147</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C118" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="D118" s="7" t="s">
-        <v>13</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="C118" s="5" t="str">
+        <f>IF($C$117&gt;=$C$80,"CUMPLE","NO CUMPLE - USAR REFUERZO SUPLEMENTARIO")</f>
+        <v>NO CUMPLE - USAR REFUERZO SUPLEMENTARIO</v>
+      </c>
+      <c r="D118" s="7"/>
       <c r="E118" s="2" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
+      <c r="K118">
+        <f>(750-50-50-12.7*4-7*25.4)/13</f>
+        <v>32.415384615384625</v>
+      </c>
     </row>
     <row r="119" spans="1:11">
       <c r="A119" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B119" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="D119" s="7"/>
+      <c r="B119" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="C119" s="4">
+        <v>420</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="E119" s="2" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
@@ -4793,20 +4800,19 @@
     </row>
     <row r="120" spans="1:11">
       <c r="A120" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C120" s="5">
-        <f>VLOOKUP($C$119,CATALOGOS!$M$2:$O$10,2,FALSE)</f>
-        <v>25.4</v>
+        <v>3</v>
+      </c>
+      <c r="B120" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="C120" s="4">
+        <v>0.75</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
@@ -4814,20 +4820,17 @@
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="C121" s="5">
-        <f>VLOOKUP($C$119,CATALOGOS!$M$2:$O$10,3,FALSE)</f>
-        <v>5.0670747909749769</v>
-      </c>
-      <c r="D121" s="7" t="s">
-        <v>273</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B121" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D121" s="7"/>
       <c r="E121" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
@@ -4835,160 +4838,160 @@
     </row>
     <row r="122" spans="1:11">
       <c r="A122" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C122" s="5">
+        <f>VLOOKUP($C$121,CATALOGOS!$M$2:$O$10,2,FALSE)</f>
+        <v>25.4</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E122" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C122" s="5">
-        <f>$C$78*1000/($C$118*$C$117*100)</f>
-        <v>84.289061241237448</v>
-      </c>
-      <c r="D122" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
     </row>
-    <row r="123" spans="1:11" ht="25">
+    <row r="123" spans="1:11">
       <c r="A123" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C123" s="5">
+        <f>VLOOKUP($C$121,CATALOGOS!$M$2:$O$10,3,FALSE)</f>
+        <v>5.0670747909749769</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="E123" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C123" s="5">
-        <f>CEILING($C$122/$C$121,1)</f>
-        <v>17</v>
-      </c>
-      <c r="D123" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>277</v>
       </c>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
-      <c r="H123" s="2" t="s">
-        <v>278</v>
-      </c>
+      <c r="H123" s="2"/>
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="2" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C124" s="5">
-        <f>MAX(($C$117*1*1*1*($C$10/105+0.6))/(23*$C$111*SQRT($C$10))*$C$120^1.5,8*$C$120,150)</f>
-        <v>382.86450649868806</v>
+        <f>$C$80*1000/($C$120*$C$119*100)</f>
+        <v>84.289061241237448</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>25</v>
+        <v>271</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" ht="25.5">
       <c r="A125" s="2" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C125" s="5">
-        <f>CEILING($C$124,50)</f>
-        <v>400</v>
+        <f>CEILING($C$124/$C$123,1)</f>
+        <v>17</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
-      <c r="H125" s="2"/>
-    </row>
-    <row r="126" spans="1:11" ht="17.649999999999999" customHeight="1">
-      <c r="A126" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="B126" s="13"/>
-      <c r="C126" s="14"/>
-      <c r="D126" s="15"/>
-      <c r="E126" s="13"/>
-      <c r="F126" s="13"/>
-      <c r="G126" s="13"/>
-      <c r="H126" s="13"/>
+      <c r="H125" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C126" s="5">
+        <f>MAX(($C$119*1*1*1*($C$10/105+0.6))/(23*$C$113*SQRT($C$10))*$C$122^1.5,8*$C$122,150)</f>
+        <v>382.86450649868806</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F126" s="2"/>
+      <c r="G126" s="2"/>
+      <c r="H126" s="2"/>
     </row>
     <row r="127" spans="1:11">
       <c r="A127" s="2" t="s">
-        <v>197</v>
+        <v>277</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C127" s="5">
-        <f>0.75*$C$91</f>
-        <v>630</v>
+        <f>CEILING($C$126,50)</f>
+        <v>400</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
     </row>
-    <row r="128" spans="1:11">
-      <c r="A128" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C128" s="5">
-        <f>0.45*$C$91</f>
-        <v>378</v>
-      </c>
-      <c r="D128" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="F128" s="2"/>
-      <c r="G128" s="2"/>
-      <c r="H128" s="2"/>
+    <row r="128" spans="1:11" ht="17.649999999999999" customHeight="1">
+      <c r="A128" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="B128" s="17"/>
+      <c r="C128" s="18"/>
+      <c r="D128" s="19"/>
+      <c r="E128" s="17"/>
+      <c r="F128" s="17"/>
+      <c r="G128" s="17"/>
+      <c r="H128" s="17"/>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C129" s="5">
-        <f>PI()*$C$88^2/4</f>
-        <v>791.73043608984017</v>
+        <f>0.75*$C$93</f>
+        <v>630</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>162</v>
+        <v>9</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
@@ -4996,20 +4999,20 @@
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="2" t="s">
-        <v>291</v>
+        <v>195</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="C130" s="5">
-        <f>$C$56*1000/($C$94*$C$129)</f>
-        <v>76.472637056539739</v>
+        <f>0.45*$C$93</f>
+        <v>378</v>
       </c>
       <c r="D130" s="7" t="s">
         <v>9</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
@@ -5017,20 +5020,20 @@
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="2" t="s">
-        <v>294</v>
+        <v>195</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C131" s="5">
-        <f>MIN(1.3*$C$127-$C$127/(0.75*$C$128)*$C$130,$C$127)</f>
-        <v>630</v>
+        <f>PI()*$C$90^2/4</f>
+        <v>791.73043608984017</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>9</v>
+        <v>160</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
@@ -5038,20 +5041,20 @@
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="C132" s="5">
-        <f>$C$92*$C$131</f>
-        <v>472.5</v>
+        <f>$C$58*1000/($C$96*$C$131)</f>
+        <v>76.472637056539739</v>
       </c>
       <c r="D132" s="7" t="s">
         <v>9</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
@@ -5059,20 +5062,20 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C133" s="5">
+        <f>MIN(1.3*$C$129-$C$129/(0.75*$C$130)*$C$132,$C$129)</f>
+        <v>630</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E133" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C133" s="5">
-        <f>($C$85+$C$27)/2</f>
-        <v>39.6875</v>
-      </c>
-      <c r="D133" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
@@ -5080,20 +5083,20 @@
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C134" s="5">
-        <f>$C$88^3/6</f>
-        <v>5334.330729166667</v>
+        <f>$C$94*$C$133</f>
+        <v>472.5</v>
       </c>
       <c r="D134" s="7" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
@@ -5101,20 +5104,20 @@
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C135" s="5">
-        <f>$C$78*1000/($C$93*$C$129)</f>
-        <v>479.07817900602726</v>
+        <f>($C$87+$C$29)/2</f>
+        <v>39.6875</v>
       </c>
       <c r="D135" s="7" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
@@ -5122,20 +5125,20 @@
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C136" s="5">
-        <f>$C$56*1000*$C$133/$C$94</f>
-        <v>2402908.0357142859</v>
+        <f>$C$90^3/6</f>
+        <v>5334.330729166667</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>306</v>
+        <v>44</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
@@ -5143,20 +5146,20 @@
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="C137" s="5">
-        <f>$C$136/$C$134</f>
-        <v>450.46101520774471</v>
+        <f>$C$80*1000/($C$95*$C$131)</f>
+        <v>479.07817900602726</v>
       </c>
       <c r="D137" s="7" t="s">
         <v>9</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
@@ -5164,20 +5167,20 @@
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C138" s="5">
-        <f>$C$135+$C$137</f>
-        <v>929.53919421377191</v>
+        <f>$C$58*1000*$C$135/$C$96</f>
+        <v>2402908.0357142859</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>9</v>
+        <v>304</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
@@ -5185,18 +5188,20 @@
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="2" t="s">
-        <v>149</v>
+        <v>292</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C139" s="5" t="str">
-        <f>IF($C$132&gt;=$C$138,"CUMPLE","NO CUMPLE")</f>
-        <v>NO CUMPLE</v>
-      </c>
-      <c r="D139" s="7"/>
+        <v>306</v>
+      </c>
+      <c r="C139" s="5">
+        <f>$C$138/$C$136</f>
+        <v>450.46101520774471</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="E139" s="2" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
@@ -5204,18 +5209,20 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="2" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C140" s="5" t="str">
-        <f>IF($C$22="Sí","Sí",IF($C$22="No","No",IF($C$139="CUMPLE","No","Sí")))</f>
-        <v>Sí</v>
-      </c>
-      <c r="D140" s="7"/>
+        <v>308</v>
+      </c>
+      <c r="C140" s="5">
+        <f>$C$137+$C$139</f>
+        <v>929.53919421377191</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="E140" s="2" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
@@ -5223,20 +5230,18 @@
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="2" t="s">
-        <v>314</v>
+        <v>147</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C141" s="5">
-        <f>IF($C$140="Sí",$C$56*1000/($C$11*0.85*$C$10*$C$23),0)</f>
-        <v>121.7611147022912</v>
-      </c>
-      <c r="D141" s="7" t="s">
-        <v>25</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="C141" s="5" t="str">
+        <f>IF($C$134&gt;=$C$140,"CUMPLE","NO CUMPLE")</f>
+        <v>NO CUMPLE</v>
+      </c>
+      <c r="D141" s="7"/>
       <c r="E141" s="2" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
@@ -5244,18 +5249,18 @@
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="2" t="s">
-        <v>149</v>
+        <v>312</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C142" s="5" t="str">
-        <f>IF($C$140="No","N/A",IF($C$24&gt;=$C$141,"CUMPLE","NO CUMPLE"))</f>
-        <v>CUMPLE</v>
+        <f>IF($C$24="Sí","Sí",IF($C$24="No","No",IF($C$141="CUMPLE","No","Sí")))</f>
+        <v>Sí</v>
       </c>
       <c r="D142" s="7"/>
       <c r="E142" s="2" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
@@ -5263,20 +5268,20 @@
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C143" s="5">
-        <f>IF($C$140="Sí",$C$56*1000*($C$17+$C$24/2),0)</f>
-        <v>89002200</v>
+        <f>IF($C$142="Sí",$C$58*1000/($C$11*0.85*$C$10*$C$25),0)</f>
+        <v>121.7611147022912</v>
       </c>
       <c r="D143" s="7" t="s">
-        <v>306</v>
+        <v>25</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
@@ -5284,241 +5289,239 @@
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="2" t="s">
-        <v>314</v>
+        <v>147</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C144" s="5">
-        <f>IF($C$140="Sí",2*SQRT($C$143/(0.9*$C$23*345)),0)</f>
-        <v>50.476973486814963</v>
-      </c>
-      <c r="D144" s="7" t="s">
-        <v>25</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="C144" s="5" t="str">
+        <f>IF($C$142="No","N/A",IF($C$26&gt;=$C$143,"CUMPLE","NO CUMPLE"))</f>
+        <v>CUMPLE</v>
+      </c>
+      <c r="D144" s="7"/>
       <c r="E144" s="2" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
     </row>
-    <row r="145" spans="1:8" ht="37.5">
+    <row r="145" spans="1:8">
       <c r="A145" s="2" t="s">
-        <v>149</v>
+        <v>312</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="C145" s="5" t="str">
-        <f>IF($C$140="No","N/A",IF($C$25&gt;=$C$144,"CUMPLE",IF(ABS($C$25-$C$144)&lt;=2,"CUMPLE - APROX. COMERCIAL","NO CUMPLE")))</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="D145" s="7"/>
+        <v>319</v>
+      </c>
+      <c r="C145" s="5">
+        <f>IF($C$142="Sí",$C$58*1000*($C$19+$C$26/2),0)</f>
+        <v>89002200</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>304</v>
+      </c>
       <c r="E145" s="2" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
-      <c r="H145" s="2" t="s">
-        <v>327</v>
-      </c>
+      <c r="H145" s="2"/>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="C146" s="5">
-        <f>IF($C$140="Sí",1*0.6*345*$C$23*$C$25/1000,0)</f>
-        <v>4732.0200000000004</v>
+        <f>IF($C$142="Sí",2*SQRT($C$145/(0.9*$C$25*345)),0)</f>
+        <v>50.476973486814963</v>
       </c>
       <c r="D146" s="7" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" ht="38.25">
       <c r="A147" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="C147" s="5" t="str">
-        <f>IF($C$140="No","N/A",IF($C$146&gt;=$C$56,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF($C$142="No","N/A",IF($C$27&gt;=$C$146,"CUMPLE",IF(ABS($C$27-$C$146)&lt;=2,"CUMPLE - APROX. COMERCIAL","NO CUMPLE")))</f>
         <v>CUMPLE</v>
       </c>
       <c r="D147" s="7"/>
       <c r="E147" s="2" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
-      <c r="H147" s="2"/>
-    </row>
-    <row r="148" spans="1:8" ht="17.649999999999999" customHeight="1">
-      <c r="A148" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="B148" s="13"/>
-      <c r="C148" s="14"/>
-      <c r="D148" s="15"/>
-      <c r="E148" s="13"/>
-      <c r="F148" s="13"/>
-      <c r="G148" s="13"/>
-      <c r="H148" s="13"/>
+      <c r="H147" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C148" s="5">
+        <f>IF($C$142="Sí",1*0.6*345*$C$25*$C$27/1000,0)</f>
+        <v>4732.0200000000004</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="F148" s="2"/>
+      <c r="G148" s="2"/>
+      <c r="H148" s="2"/>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="2" t="s">
-        <v>333</v>
+        <v>147</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="C149" s="5">
-        <f>$C$32-2*$C$36</f>
-        <v>390</v>
-      </c>
-      <c r="D149" s="7" t="s">
-        <v>25</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="C149" s="5" t="str">
+        <f>IF($C$142="No","N/A",IF($C$148&gt;=$C$58,"CUMPLE","NO CUMPLE"))</f>
+        <v>CUMPLE</v>
+      </c>
+      <c r="D149" s="7"/>
       <c r="E149" s="2" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
     </row>
-    <row r="150" spans="1:8">
-      <c r="A150" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="C150" s="5">
-        <f>$C$56*1000/(0.318*2*$C$149*$C$18)</f>
-        <v>7.0460866803990712</v>
-      </c>
-      <c r="D150" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="F150" s="2"/>
-      <c r="G150" s="2"/>
-      <c r="H150" s="2"/>
+    <row r="150" spans="1:8" ht="17.649999999999999" customHeight="1">
+      <c r="A150" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="B150" s="17"/>
+      <c r="C150" s="18"/>
+      <c r="D150" s="19"/>
+      <c r="E150" s="17"/>
+      <c r="F150" s="17"/>
+      <c r="G150" s="17"/>
+      <c r="H150" s="17"/>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="2" t="s">
-        <v>3</v>
+        <v>331</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="C151" s="4">
-        <v>9.5</v>
+        <v>332</v>
+      </c>
+      <c r="C151" s="5">
+        <f>$C$34-2*$C$38</f>
+        <v>390</v>
       </c>
       <c r="D151" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
-      <c r="H151" s="2" t="s">
-        <v>340</v>
-      </c>
+      <c r="H151" s="2"/>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="2" t="s">
-        <v>149</v>
+        <v>331</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C152" s="5" t="str">
-        <f>IF($C$151&gt;=MAX($C$150,8),"CUMPLE","NO CUMPLE")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="D152" s="7"/>
+        <v>334</v>
+      </c>
+      <c r="C152" s="5">
+        <f>$C$58*1000/(0.318*2*$C$151*$C$20)</f>
+        <v>7.0460866803990712</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="E152" s="2" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
-      <c r="H152" s="2" t="s">
-        <v>343</v>
-      </c>
+      <c r="H152" s="2"/>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C153" s="5">
-        <f>VLOOKUP($C$88,CATALOGOS!$A$2:$G$10,5,FALSE)</f>
-        <v>34.340000000000003</v>
+        <v>3</v>
+      </c>
+      <c r="B153" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="C153" s="4">
+        <v>9.5</v>
       </c>
       <c r="D153" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
-      <c r="H153" s="2"/>
+      <c r="H153" s="2" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="2" t="s">
-        <v>344</v>
+        <v>147</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C154" s="5">
-        <f>$C$56/$C$94</f>
-        <v>60.545714285714283</v>
-      </c>
-      <c r="D154" s="7" t="s">
-        <v>101</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="C154" s="5" t="str">
+        <f>IF($C$153&gt;=MAX($C$152,8),"CUMPLE","NO CUMPLE")</f>
+        <v>CUMPLE</v>
+      </c>
+      <c r="D154" s="7"/>
       <c r="E154" s="2" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
-      <c r="H154" s="2"/>
+      <c r="H154" s="2" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C155" s="5">
-        <f>($C$26-$C$153)/2</f>
-        <v>27.83</v>
+        <f>VLOOKUP($C$90,CATALOGOS!$A$2:$G$10,5,FALSE)</f>
+        <v>34.340000000000003</v>
       </c>
       <c r="D155" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
@@ -5526,41 +5529,41 @@
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C156" s="5">
-        <f>0.75*1.5*$C$155*$C$27*$C$9/1000</f>
-        <v>222.66782999999995</v>
+        <f>$C$58/$C$96</f>
+        <v>60.545714285714283</v>
       </c>
       <c r="D156" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
-      <c r="H156" s="2" t="s">
-        <v>353</v>
-      </c>
+      <c r="H156" s="2"/>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="2" t="s">
-        <v>149</v>
+        <v>342</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="C157" s="5" t="str">
-        <f>IF($C$156&gt;=$C$154,"CUMPLE","NO CUMPLE")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="D157" s="7"/>
+        <v>347</v>
+      </c>
+      <c r="C157" s="5">
+        <f>($C$28-$C$155)/2</f>
+        <v>27.83</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="E157" s="2" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
@@ -5568,41 +5571,41 @@
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="2" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="C158" s="5">
-        <f>2*$C$26</f>
-        <v>180</v>
+        <f>0.75*1.5*$C$157*$C$29*$C$9/1000</f>
+        <v>222.66782999999995</v>
       </c>
       <c r="D158" s="7" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
-      <c r="H158" s="2"/>
+      <c r="H158" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="2" t="s">
-        <v>356</v>
+        <v>147</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C159" s="5">
-        <f>$C$154*1000/(0.318*$C$158*$C$18)</f>
-        <v>2.1809315915520933</v>
-      </c>
-      <c r="D159" s="7" t="s">
-        <v>25</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="C159" s="5" t="str">
+        <f>IF($C$158&gt;=$C$156,"CUMPLE","NO CUMPLE")</f>
+        <v>CUMPLE</v>
+      </c>
+      <c r="D159" s="7"/>
       <c r="E159" s="2" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
@@ -5610,18 +5613,20 @@
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="2" t="s">
-        <v>149</v>
+        <v>354</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C160" s="5" t="str">
-        <f>IF($C$28&gt;=MAX($C$159,6.35),"CUMPLE","NO CUMPLE")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="D160" s="7"/>
+        <v>355</v>
+      </c>
+      <c r="C160" s="5">
+        <f>2*$C$28</f>
+        <v>180</v>
+      </c>
+      <c r="D160" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="E160" s="2" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
@@ -5629,20 +5634,20 @@
     </row>
     <row r="161" spans="1:8">
       <c r="A161" s="2" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C161" s="5">
-        <f>$C$78/$C$93</f>
-        <v>379.30077558556849</v>
+        <f>$C$156*1000/(0.318*$C$160*$C$20)</f>
+        <v>2.1809315915520933</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
@@ -5650,20 +5655,18 @@
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="2" t="s">
-        <v>363</v>
+        <v>147</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="C162" s="5">
-        <f>VLOOKUP($C$88,CATALOGOS!$A$2:$G$10,7,FALSE)</f>
-        <v>47.63</v>
-      </c>
-      <c r="D162" s="7" t="s">
-        <v>25</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="C162" s="5" t="str">
+        <f>IF($C$30&gt;=MAX($C$161,6.35),"CUMPLE","NO CUMPLE")</f>
+        <v>CUMPLE</v>
+      </c>
+      <c r="D162" s="7"/>
       <c r="E162" s="2" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
@@ -5671,20 +5674,20 @@
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C163" s="5">
+        <f>$C$80/$C$95</f>
+        <v>379.30077558556849</v>
+      </c>
+      <c r="D163" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E163" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C163" s="5">
-        <f>$C$29/2-$C$162/2</f>
-        <v>21.184999999999999</v>
-      </c>
-      <c r="D163" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E163" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
@@ -5692,20 +5695,20 @@
     </row>
     <row r="164" spans="1:8">
       <c r="A164" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C164" s="5">
-        <f>PI()*$C$153^2/4</f>
-        <v>926.16947445288815</v>
+        <f>VLOOKUP($C$90,CATALOGOS!$A$2:$G$10,7,FALSE)</f>
+        <v>47.63</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>162</v>
+        <v>25</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
@@ -5713,20 +5716,20 @@
     </row>
     <row r="165" spans="1:8">
       <c r="A165" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C165" s="5">
-        <f>$C$29-$C$153</f>
-        <v>55.66</v>
+        <f>$C$31/2-$C$164/2</f>
+        <v>21.184999999999999</v>
       </c>
       <c r="D165" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
@@ -5734,20 +5737,20 @@
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C166" s="5">
-        <f>$C$161*1000*$C$29/($C$29^2-$C$164)</f>
-        <v>4758.55537444519</v>
+        <f>PI()*$C$155^2/4</f>
+        <v>926.16947445288815</v>
       </c>
       <c r="D166" s="7" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
@@ -5755,20 +5758,20 @@
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C167" s="5">
-        <f>$C$166*$C$163^2/2</f>
-        <v>1067829.8784737291</v>
+        <f>$C$31-$C$155</f>
+        <v>55.66</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>306</v>
+        <v>25</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
@@ -5776,20 +5779,20 @@
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C168" s="5">
-        <f>0.9*$C$165*$C$30^2*345/6</f>
-        <v>1422777.8500031251</v>
+        <f>$C$163*1000*$C$31/($C$31^2-$C$166)</f>
+        <v>4758.55537444519</v>
       </c>
       <c r="D168" s="7" t="s">
-        <v>306</v>
+        <v>131</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
@@ -5797,18 +5800,20 @@
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="2" t="s">
-        <v>149</v>
+        <v>361</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="C169" s="5" t="str">
-        <f>IF($C$167&lt;=$C$168,"CUMPLE","NO CUMPLE")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="D169" s="7"/>
+        <v>373</v>
+      </c>
+      <c r="C169" s="5">
+        <f>$C$168*$C$165^2/2</f>
+        <v>1067829.8784737291</v>
+      </c>
+      <c r="D169" s="7" t="s">
+        <v>304</v>
+      </c>
       <c r="E169" s="2" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
@@ -5816,20 +5821,20 @@
     </row>
     <row r="170" spans="1:8">
       <c r="A170" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C170" s="5">
-        <f>$C$166*$C$163</f>
-        <v>100809.99560762134</v>
+        <f>0.9*$C$167*$C$32^2*345/6</f>
+        <v>1422777.8500031251</v>
       </c>
       <c r="D170" s="7" t="s">
-        <v>382</v>
+        <v>304</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
@@ -5837,20 +5842,18 @@
     </row>
     <row r="171" spans="1:8">
       <c r="A171" s="2" t="s">
-        <v>363</v>
+        <v>147</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="C171" s="5">
-        <f>1*0.6*$C$165*$C$30*345</f>
-        <v>256068.00449999995</v>
-      </c>
-      <c r="D171" s="7" t="s">
-        <v>382</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="C171" s="5" t="str">
+        <f>IF($C$169&lt;=$C$170,"CUMPLE","NO CUMPLE")</f>
+        <v>CUMPLE</v>
+      </c>
+      <c r="D171" s="7"/>
       <c r="E171" s="2" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
@@ -5858,144 +5861,148 @@
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="2" t="s">
-        <v>149</v>
+        <v>361</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="C172" s="5" t="str">
-        <f>IF($C$170&lt;=$C$171,"CUMPLE","NO CUMPLE")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="D172" s="7"/>
+        <v>379</v>
+      </c>
+      <c r="C172" s="5">
+        <f>$C$168*$C$165</f>
+        <v>100809.99560762134</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>380</v>
+      </c>
       <c r="E172" s="2" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
     </row>
-    <row r="173" spans="1:8" ht="17.649999999999999" customHeight="1">
-      <c r="A173" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="B173" s="13"/>
-      <c r="C173" s="14"/>
-      <c r="D173" s="15"/>
-      <c r="E173" s="13"/>
-      <c r="F173" s="13"/>
-      <c r="G173" s="13"/>
-      <c r="H173" s="13"/>
+    <row r="173" spans="1:8">
+      <c r="A173" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C173" s="5">
+        <f>1*0.6*$C$167*$C$32*345</f>
+        <v>256068.00449999995</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F173" s="2"/>
+      <c r="G173" s="2"/>
+      <c r="H173" s="2"/>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="2" t="s">
-        <v>389</v>
+        <v>147</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C174" s="5" t="str">
-        <f>$C$86</f>
+        <f>IF($C$172&lt;=$C$173,"CUMPLE","NO CUMPLE")</f>
         <v>CUMPLE</v>
       </c>
       <c r="D174" s="7"/>
       <c r="E174" s="2" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
     </row>
-    <row r="175" spans="1:8">
-      <c r="A175" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="C175" s="5" t="str">
-        <f>$C$98</f>
+    <row r="175" spans="1:8" ht="17.649999999999999" customHeight="1">
+      <c r="A175" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="B175" s="17"/>
+      <c r="C175" s="18"/>
+      <c r="D175" s="19"/>
+      <c r="E175" s="17"/>
+      <c r="F175" s="17"/>
+      <c r="G175" s="17"/>
+      <c r="H175" s="17"/>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="A176" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C176" s="5" t="str">
+        <f>$C$88</f>
         <v>CUMPLE</v>
-      </c>
-      <c r="D175" s="7"/>
-      <c r="E175" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F175" s="2"/>
-      <c r="G175" s="2"/>
-      <c r="H175" s="2"/>
-    </row>
-    <row r="176" spans="1:8" ht="39">
-      <c r="A176" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C176" s="5" t="str">
-        <f>IF(LEFT($C$116,6)="CUMPLE","CUMPLE POR CONCRETO","CUMPLE CON REFUERZO SUPLEMENTARIO")</f>
-        <v>CUMPLE CON REFUERZO SUPLEMENTARIO</v>
       </c>
       <c r="D176" s="7"/>
       <c r="E176" s="2" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
     </row>
-    <row r="177" spans="1:8" ht="26">
+    <row r="177" spans="1:8">
       <c r="A177" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C177" s="5" t="str">
-        <f>IF($C$139="CUMPLE","CUMPLE",IF($C$140="Sí","CUMPLE CON LLAVE DE CORTE","NO CUMPLE"))</f>
-        <v>CUMPLE CON LLAVE DE CORTE</v>
+        <f>$C$100</f>
+        <v>CUMPLE</v>
       </c>
       <c r="D177" s="7"/>
       <c r="E177" s="2" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:8" ht="38.25">
       <c r="A178" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="C178" s="5" t="str">
-        <f>IF($C$140="No","NO REQUERIDA",IF(AND(LEFT($C$142,6)="CUMPLE",LEFT($C$145,6)="CUMPLE",LEFT($C$147,6)="CUMPLE"),"CUMPLE","NO CUMPLE"))</f>
-        <v>CUMPLE</v>
+        <f>IF(LEFT($C$118,6)="CUMPLE","CUMPLE POR CONCRETO","CUMPLE CON REFUERZO SUPLEMENTARIO")</f>
+        <v>CUMPLE CON REFUERZO SUPLEMENTARIO</v>
       </c>
       <c r="D178" s="7"/>
       <c r="E178" s="2" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" ht="25.5">
       <c r="A179" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C179" s="5" t="str">
-        <f>$C$152</f>
-        <v>CUMPLE</v>
+        <f>IF($C$141="CUMPLE","CUMPLE",IF($C$142="Sí","CUMPLE CON LLAVE DE CORTE","NO CUMPLE"))</f>
+        <v>CUMPLE CON LLAVE DE CORTE</v>
       </c>
       <c r="D179" s="7"/>
       <c r="E179" s="2" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
@@ -6003,18 +6010,18 @@
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C180" s="5" t="str">
-        <f>$C$157</f>
+        <f>IF($C$142="No","NO REQUERIDA",IF(AND(LEFT($C$144,6)="CUMPLE",LEFT($C$147,6)="CUMPLE",LEFT($C$149,6)="CUMPLE"),"CUMPLE","NO CUMPLE"))</f>
         <v>CUMPLE</v>
       </c>
       <c r="D180" s="7"/>
       <c r="E180" s="2" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
@@ -6022,58 +6029,96 @@
     </row>
     <row r="181" spans="1:8">
       <c r="A181" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C181" s="5" t="str">
-        <f>IF(AND($C$169="CUMPLE",$C$172="CUMPLE"),"CUMPLE","NO CUMPLE")</f>
+        <f>$C$154</f>
         <v>CUMPLE</v>
       </c>
       <c r="D181" s="7"/>
       <c r="E181" s="2" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
     </row>
-    <row r="182" spans="1:8" ht="26">
+    <row r="182" spans="1:8">
       <c r="A182" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C182" s="5" t="str">
-        <f>IF(AND(LEFT($C$174,6)="CUMPLE",LEFT($C$175,6)="CUMPLE",LEFT($C$176,6)="CUMPLE",LEFT($C$177,6)="CUMPLE",$C$178&lt;&gt;"NO CUMPLE",LEFT($C$179,6)="CUMPLE",LEFT($C$180,6)="CUMPLE",LEFT($C$181,6)="CUMPLE"),"CUMPLE - REVISAR DETALLE FINAL","NO CUMPLE / AJUSTAR VARIABLES")</f>
-        <v>CUMPLE - REVISAR DETALLE FINAL</v>
+        <f>$C$159</f>
+        <v>CUMPLE</v>
       </c>
       <c r="D182" s="7"/>
       <c r="E182" s="2" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
     </row>
+    <row r="183" spans="1:8">
+      <c r="A183" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C183" s="5" t="str">
+        <f>IF(AND($C$171="CUMPLE",$C$174="CUMPLE"),"CUMPLE","NO CUMPLE")</f>
+        <v>CUMPLE</v>
+      </c>
+      <c r="D183" s="7"/>
+      <c r="E183" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F183" s="2"/>
+      <c r="G183" s="2"/>
+      <c r="H183" s="2"/>
+    </row>
+    <row r="184" spans="1:8" ht="25.5">
+      <c r="A184" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C184" s="5" t="str">
+        <f>IF(AND(LEFT($C$176,6)="CUMPLE",LEFT($C$177,6)="CUMPLE",LEFT($C$178,6)="CUMPLE",LEFT($C$179,6)="CUMPLE",$C$180&lt;&gt;"NO CUMPLE",LEFT($C$181,6)="CUMPLE",LEFT($C$182,6)="CUMPLE",LEFT($C$183,6)="CUMPLE"),"CUMPLE - REVISAR DETALLE FINAL","NO CUMPLE / AJUSTAR VARIABLES")</f>
+        <v>CUMPLE - REVISAR DETALLE FINAL</v>
+      </c>
+      <c r="D184" s="7"/>
+      <c r="E184" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="F184" s="2"/>
+      <c r="G184" s="2"/>
+      <c r="H184" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A150:H150"/>
+    <mergeCell ref="A175:H175"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A89:H89"/>
+    <mergeCell ref="A101:H101"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A126:H126"/>
-    <mergeCell ref="A148:H148"/>
-    <mergeCell ref="A173:H173"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A87:H87"/>
-    <mergeCell ref="A99:H99"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A128:H128"/>
   </mergeCells>
-  <conditionalFormatting sqref="C1:C182">
+  <conditionalFormatting sqref="C1:C184">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>LEFT(C1,9)="NO CUMPLE"</formula>
     </cfRule>
@@ -6090,7 +6135,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="8">
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>PERFILES!$B$3:$B$125</xm:f>
@@ -6101,43 +6146,43 @@
           <x14:formula1>
             <xm:f>CATALOGOS!$Q$2:$Q$3</xm:f>
           </x14:formula1>
-          <xm:sqref>C21</xm:sqref>
+          <xm:sqref>C23</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>CATALOGOS!$S$2:$S$4</xm:f>
           </x14:formula1>
-          <xm:sqref>C22</xm:sqref>
+          <xm:sqref>C24</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000003000000}">
           <x14:formula1>
             <xm:f>CATALOGOS!$I$2:$I$18</xm:f>
           </x14:formula1>
-          <xm:sqref>C85 C30 C27 C25</xm:sqref>
+          <xm:sqref>C87 C32 C29 C27</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000007000000}">
           <x14:formula1>
             <xm:f>CATALOGOS!$A$2:$A$10</xm:f>
           </x14:formula1>
-          <xm:sqref>C88</xm:sqref>
+          <xm:sqref>C90</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000008000000}">
           <x14:formula1>
             <xm:f>CATALOGOS!$M$2:$M$10</xm:f>
           </x14:formula1>
-          <xm:sqref>C119</xm:sqref>
+          <xm:sqref>C121</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000009000000}">
           <x14:formula1>
             <xm:f>CATALOGOS!$U$2:$U$8</xm:f>
           </x14:formula1>
-          <xm:sqref>C26</xm:sqref>
+          <xm:sqref>C28</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-00000A000000}">
           <x14:formula1>
             <xm:f>CATALOGOS!$W$2:$W$8</xm:f>
           </x14:formula1>
-          <xm:sqref>C151 C28</xm:sqref>
+          <xm:sqref>C153 C30</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6148,98 +6193,98 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AC200"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="29" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:29" ht="15">
       <c r="A1" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="D1" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>410</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="G1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="J1" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="K1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>413</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>415</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>416</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="S1" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="V1" s="8" t="s">
         <v>422</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="W1" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="X1" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="Y1" s="8" t="s">
         <v>425</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="Z1" s="8" t="s">
         <v>426</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="AA1" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="Z1" s="8" t="s">
+      <c r="AB1" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AC1" s="8" t="s">
         <v>429</v>
-      </c>
-      <c r="AB1" s="8" t="s">
-        <v>430</v>
-      </c>
-      <c r="AC1" s="8" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="2" spans="1:29">
@@ -6250,85 +6295,85 @@
         <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="T2" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="Z2" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="R2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="V2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="AC2" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -6387,7 +6432,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C4" s="1">
         <v>764.34</v>
@@ -6476,7 +6521,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C5" s="1">
         <v>1032.3216</v>
@@ -6565,7 +6610,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C6" s="1">
         <v>1321.0216</v>
@@ -6654,7 +6699,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C7" s="1">
         <v>1642.6016</v>
@@ -6743,7 +6788,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C8" s="1">
         <v>2009.1304000000002</v>
@@ -6832,7 +6877,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C9" s="1">
         <v>2394.7303999999999</v>
@@ -6921,7 +6966,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C10" s="1">
         <v>2848.4096</v>
@@ -7010,7 +7055,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C11" s="1">
         <v>3337.0495999999994</v>
@@ -7099,7 +7144,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C12" s="1">
         <v>3911.62</v>
@@ -7188,7 +7233,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C13" s="1">
         <v>4594.5</v>
@@ -7277,7 +7322,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C14" s="1">
         <v>5381.2000000000007</v>
@@ -7366,7 +7411,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C15" s="1">
         <v>6260.6216000000004</v>
@@ -7455,7 +7500,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C16" s="1">
         <v>7272.9216000000006</v>
@@ -7544,7 +7589,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C17" s="1">
         <v>8446.3544000000002</v>
@@ -7633,7 +7678,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C18" s="1">
         <v>9882.0744000000013</v>
@@ -7722,7 +7767,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C19" s="1">
         <v>11552.154399999999</v>
@@ -7811,7 +7856,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C20" s="1">
         <v>13441.598399999999</v>
@@ -7900,7 +7945,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C21" s="1">
         <v>15598.438399999999</v>
@@ -7989,7 +8034,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C22" s="1">
         <v>17458.577600000001</v>
@@ -8078,7 +8123,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C23" s="1">
         <v>18748.8776</v>
@@ -8167,7 +8212,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C24" s="1">
         <v>2123.6095999999998</v>
@@ -8256,7 +8301,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C25" s="1">
         <v>2603.6095999999998</v>
@@ -8345,7 +8390,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C26" s="1">
         <v>2533.6095999999998</v>
@@ -8434,7 +8479,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C27" s="1">
         <v>3400.6095999999998</v>
@@ -8523,7 +8568,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C28" s="1">
         <v>3141.6095999999998</v>
@@ -8612,7 +8657,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C29" s="1">
         <v>4295.6095999999998</v>
@@ -8701,7 +8746,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C30" s="1">
         <v>3877.14</v>
@@ -8790,7 +8835,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C31" s="1">
         <v>5425.14</v>
@@ -8879,7 +8924,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C32" s="1">
         <v>4525.1400000000003</v>
@@ -8968,7 +9013,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C33" s="1">
         <v>6525.14</v>
@@ -9057,7 +9102,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C34" s="1">
         <v>5383.1216000000004</v>
@@ -9146,7 +9191,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C35" s="1">
         <v>7808.1216000000004</v>
@@ -9235,7 +9280,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C36" s="1">
         <v>6434.1216000000004</v>
@@ -9324,7 +9369,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C37" s="1">
         <v>9104.1216000000004</v>
@@ -9413,7 +9458,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C38" s="1">
         <v>7683.5544</v>
@@ -9502,7 +9547,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C39" s="1">
         <v>10598.554400000001</v>
@@ -9591,7 +9636,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C40" s="1">
         <v>8681.9383999999991</v>
@@ -9680,7 +9725,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C41" s="1">
         <v>11844.438399999999</v>
@@ -9769,7 +9814,7 @@
         <v>39</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C42" s="1">
         <v>9726.4383999999991</v>
@@ -9858,7 +9903,7 @@
         <v>40</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C43" s="1">
         <v>13136.438399999999</v>
@@ -9947,7 +9992,7 @@
         <v>41</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C44" s="1">
         <v>11255.3236</v>
@@ -10036,7 +10081,7 @@
         <v>42</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C45" s="1">
         <v>14907.7736</v>
@@ -10125,7 +10170,7 @@
         <v>43</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C46" s="1">
         <v>12436.7736</v>
@@ -10214,7 +10259,7 @@
         <v>44</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C47" s="1">
         <v>16134.2736</v>
@@ -10303,7 +10348,7 @@
         <v>45</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C48" s="1">
         <v>13347.2736</v>
@@ -10392,7 +10437,7 @@
         <v>46</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C49" s="1">
         <v>17089.7736</v>
@@ -10481,7 +10526,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C50" s="1">
         <v>14275.7736</v>
@@ -10570,7 +10615,7 @@
         <v>48</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C51" s="1">
         <v>18063.2736</v>
@@ -10659,7 +10704,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C52" s="1">
         <v>15897.7736</v>
@@ -10748,7 +10793,7 @@
         <v>50</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C53" s="1">
         <v>19777.7736</v>
@@ -10837,7 +10882,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C54" s="1">
         <v>17802.7736</v>
@@ -10926,7 +10971,7 @@
         <v>52</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C55" s="1">
         <v>21797.7736</v>
@@ -11015,7 +11060,7 @@
         <v>53</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C56" s="1">
         <v>19753.7736</v>
@@ -11104,7 +11149,7 @@
         <v>54</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C57" s="1">
         <v>23863.7736</v>
@@ -11193,7 +11238,7 @@
         <v>55</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C58" s="1">
         <v>21175.7736</v>
@@ -11282,7 +11327,7 @@
         <v>56</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C59" s="1">
         <v>25405.7736</v>
@@ -11371,7 +11416,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C60" s="1">
         <v>22645.7736</v>
@@ -11460,7 +11505,7 @@
         <v>58</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C61" s="1">
         <v>26995.7736</v>
@@ -11549,7 +11594,7 @@
         <v>59</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C62" s="1">
         <v>24163.7736</v>
@@ -11638,7 +11683,7 @@
         <v>60</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C63" s="1">
         <v>28633.7736</v>
@@ -11727,7 +11772,7 @@
         <v>61</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C64" s="1">
         <v>26047.7736</v>
@@ -11816,7 +11861,7 @@
         <v>62</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C65" s="1">
         <v>30637.7736</v>
@@ -11905,7 +11950,7 @@
         <v>63</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C66" s="1">
         <v>28582.560000000001</v>
@@ -11994,7 +12039,7 @@
         <v>64</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C67" s="1">
         <v>33417.56</v>
@@ -12083,7 +12128,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C68" s="1">
         <v>33712.559999999998</v>
@@ -12172,7 +12217,7 @@
         <v>66</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C69" s="1">
         <v>37127.56</v>
@@ -12261,7 +12306,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C70" s="1">
         <v>34684.559999999998</v>
@@ -12350,7 +12395,7 @@
         <v>68</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C71" s="1">
         <v>40004.559999999998</v>
@@ -12439,7 +12484,7 @@
         <v>69</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C72" s="1">
         <v>37447.360000000001</v>
@@ -12528,7 +12573,7 @@
         <v>70</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C73" s="1">
         <v>42503.360000000001</v>
@@ -12617,7 +12662,7 @@
         <v>71</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C74" s="1">
         <v>1622.6096579999999</v>
@@ -12706,7 +12751,7 @@
         <v>72</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C75" s="1">
         <v>2855.8329979999999</v>
@@ -12795,7 +12840,7 @@
         <v>73</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C76" s="1">
         <v>3787.3795219999993</v>
@@ -12884,7 +12929,7 @@
         <v>74</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C77" s="1">
         <v>1912.4194009600001</v>
@@ -12973,7 +13018,7 @@
         <v>75</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C78" s="1">
         <v>2475.9021449599995</v>
@@ -13062,7 +13107,7 @@
         <v>76</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C79" s="1">
         <v>2866.0949129599994</v>
@@ -13151,7 +13196,7 @@
         <v>77</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C80" s="1">
         <v>4567.8002723811833</v>
@@ -13240,7 +13285,7 @@
         <v>78</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C81" s="1">
         <v>5320.9600563811828</v>
@@ -13329,7 +13374,7 @@
         <v>79</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C82" s="1">
         <v>5887.2815043811834</v>
@@ -13418,7 +13463,7 @@
         <v>80</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C83" s="1">
         <v>6634.4090423811822</v>
@@ -13507,7 +13552,7 @@
         <v>81</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C84" s="1">
         <v>2281.2573729599999</v>
@@ -13596,7 +13641,7 @@
         <v>82</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C85" s="1">
         <v>3218.9974329599995</v>
@@ -13685,7 +13730,7 @@
         <v>83</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C86" s="1">
         <v>3616.4805089599995</v>
@@ -13774,7 +13819,7 @@
         <v>84</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C87" s="1">
         <v>4188.6729129599989</v>
@@ -13863,7 +13908,7 @@
         <v>85</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C88" s="1">
         <v>9312.1104080000005</v>
@@ -13952,7 +13997,7 @@
         <v>86</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C89" s="1">
         <v>2679.8372209599997</v>
@@ -14041,7 +14086,7 @@
         <v>87</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C90" s="1">
         <v>3042.1590769599998</v>
@@ -14130,7 +14175,7 @@
         <v>88</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C91" s="1">
         <v>4180.4793809600005</v>
@@ -14219,7 +14264,7 @@
         <v>89</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C92" s="1">
         <v>4929.5746569599996</v>
@@ -14308,7 +14353,7 @@
         <v>90</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C93" s="1">
         <v>12303.843172909599</v>
@@ -14397,7 +14442,7 @@
         <v>91</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C94" s="1">
         <v>13614.052771839999</v>
@@ -14486,7 +14531,7 @@
         <v>92</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C95" s="1">
         <v>4183.37485904</v>
@@ -14575,7 +14620,7 @@
         <v>93</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C96" s="1">
         <v>5701.6298870400005</v>
@@ -14664,7 +14709,7 @@
         <v>94</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C97" s="1">
         <v>12845.915624246398</v>
@@ -14753,7 +14798,7 @@
         <v>95</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C98" s="1">
         <v>14093.129916909598</v>
@@ -14842,7 +14887,7 @@
         <v>96</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C99" s="1">
         <v>17054.303955839998</v>
@@ -14931,7 +14976,7 @@
         <v>97</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C100" s="1">
         <v>22832.744011839994</v>
@@ -15020,7 +15065,7 @@
         <v>98</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C101" s="1">
         <v>27535.831379840001</v>
@@ -15109,7 +15154,7 @@
         <v>99</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C102" s="1">
         <v>4958.8422588117746</v>
@@ -15198,7 +15243,7 @@
         <v>100</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C103" s="1">
         <v>5893.937162811776</v>
@@ -15287,7 +15332,7 @@
         <v>101</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C104" s="1">
         <v>6830.2578708117753</v>
@@ -15376,7 +15421,7 @@
         <v>102</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C105" s="1">
         <v>8553.8995848117756</v>
@@ -15465,7 +15510,7 @@
         <v>103</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C106" s="1">
         <v>6641.096958811775</v>
@@ -15554,7 +15599,7 @@
         <v>104</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C107" s="1">
         <v>7591.9015088117749</v>
@@ -15643,7 +15688,7 @@
         <v>105</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C108" s="1">
         <v>9467.0913068117752</v>
@@ -15732,7 +15777,7 @@
         <v>106</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C109" s="1">
         <v>8383.5961359999983</v>
@@ -15821,7 +15866,7 @@
         <v>107</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C110" s="1">
         <v>9486.0542278535995</v>
@@ -15910,7 +15955,7 @@
         <v>108</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C111" s="1">
         <v>10813.913855999999</v>
@@ -15999,7 +16044,7 @@
         <v>109</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C112" s="1">
         <v>12924.305415853598</v>
@@ -16088,7 +16133,7 @@
         <v>110</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C113" s="1">
         <v>10465.8264618536</v>
@@ -16177,7 +16222,7 @@
         <v>111</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C114" s="1">
         <v>11745.395863999998</v>
@@ -16266,7 +16311,7 @@
         <v>112</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C115" s="1">
         <v>12944.337633853598</v>
@@ -16355,7 +16400,7 @@
         <v>113</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C116" s="1">
         <v>14424.874376000002</v>
@@ -16444,7 +16489,7 @@
         <v>114</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C117" s="1">
         <v>15941.000375999998</v>
@@ -16533,7 +16578,7 @@
         <v>115</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C118" s="1">
         <v>22196.471736</v>
@@ -16622,7 +16667,7 @@
         <v>116</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C119" s="1">
         <v>24931.240459999994</v>
@@ -16711,7 +16756,7 @@
         <v>117</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C120" s="1">
         <v>10875.949600000002</v>
@@ -16800,7 +16845,7 @@
         <v>118</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C121" s="1">
         <v>15874.019999999997</v>
@@ -16889,7 +16934,7 @@
         <v>119</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C122" s="1">
         <v>16577.14</v>
@@ -16978,7 +17023,7 @@
         <v>120</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C123" s="1">
         <v>18769.14</v>
@@ -17067,7 +17112,7 @@
         <v>121</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C124" s="1">
         <v>20993.14</v>
@@ -17156,7 +17201,7 @@
         <v>122</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C125" s="1">
         <v>27857.14</v>
@@ -19576,107 +19621,107 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AC200"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="6.58203125" customWidth="1"/>
+    <col min="1" max="1" width="6.625" customWidth="1"/>
     <col min="2" max="2" width="6.75" customWidth="1"/>
-    <col min="3" max="3" width="6.83203125" customWidth="1"/>
+    <col min="3" max="3" width="6.875" customWidth="1"/>
     <col min="4" max="4" width="11.25" customWidth="1"/>
     <col min="5" max="5" width="14.25" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.08203125" customWidth="1"/>
-    <col min="9" max="9" width="5.33203125" customWidth="1"/>
+    <col min="6" max="6" width="10.875" customWidth="1"/>
+    <col min="7" max="7" width="10.125" customWidth="1"/>
+    <col min="9" max="9" width="5.375" customWidth="1"/>
     <col min="10" max="10" width="7.25" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
     <col min="13" max="13" width="4.25" customWidth="1"/>
     <col min="14" max="14" width="6.75" customWidth="1"/>
-    <col min="15" max="15" width="10.33203125" customWidth="1"/>
-    <col min="17" max="17" width="4.58203125" customWidth="1"/>
+    <col min="15" max="15" width="10.375" customWidth="1"/>
+    <col min="17" max="17" width="4.625" customWidth="1"/>
     <col min="19" max="19" width="9.25" customWidth="1"/>
-    <col min="21" max="21" width="16.33203125" customWidth="1"/>
+    <col min="21" max="21" width="16.375" customWidth="1"/>
     <col min="23" max="23" width="18.75" customWidth="1"/>
-    <col min="25" max="25" width="13.83203125" customWidth="1"/>
-    <col min="26" max="26" width="5.83203125" customWidth="1"/>
-    <col min="27" max="27" width="6.08203125" customWidth="1"/>
+    <col min="25" max="25" width="13.875" customWidth="1"/>
+    <col min="26" max="26" width="5.875" customWidth="1"/>
+    <col min="27" max="27" width="6.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="28">
+    <row r="1" spans="1:29" ht="30">
       <c r="A1" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>561</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>563</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>564</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>565</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>566</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>567</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="8" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="L1" s="8"/>
       <c r="M1" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="O1" s="8" t="s">
         <v>570</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>571</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>572</v>
       </c>
       <c r="P1" s="8"/>
       <c r="Q1" s="8" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="R1" s="8"/>
       <c r="S1" s="8" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="T1" s="8"/>
       <c r="U1" s="8" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="V1" s="8"/>
       <c r="W1" s="8" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="X1" s="8"/>
       <c r="Y1" s="8" t="s">
+        <v>575</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="AA1" s="8" t="s">
         <v>577</v>
-      </c>
-      <c r="Z1" s="8" t="s">
-        <v>578</v>
-      </c>
-      <c r="AA1" s="8" t="s">
-        <v>579</v>
       </c>
       <c r="AB1" s="8"/>
       <c r="AC1" s="8"/>
     </row>
-    <row r="2" spans="1:29" ht="28">
+    <row r="2" spans="1:29" ht="28.5">
       <c r="A2" s="1">
         <v>19.05</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C2" s="1">
         <v>0.75</v>
@@ -19701,11 +19746,11 @@
         <v>0.25</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="N2" s="1">
         <v>6.35</v>
@@ -19715,11 +19760,11 @@
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T2" s="1"/>
       <c r="U2" s="1">
@@ -19731,7 +19776,7 @@
       </c>
       <c r="X2" s="1"/>
       <c r="Y2" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="Z2" s="1">
         <v>248</v>
@@ -19742,12 +19787,12 @@
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
     </row>
-    <row r="3" spans="1:29" ht="28">
+    <row r="3" spans="1:29" ht="28.5">
       <c r="A3" s="1">
         <v>22.225000000000001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C3" s="1">
         <v>0.875</v>
@@ -19772,11 +19817,11 @@
         <v>0.315</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="N3" s="1">
         <v>9.5250000000000004</v>
@@ -19786,11 +19831,11 @@
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="R3" s="1"/>
       <c r="S3" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1">
@@ -19802,7 +19847,7 @@
       </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="Z3" s="1">
         <v>345</v>
@@ -19818,7 +19863,7 @@
         <v>25.4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -19843,11 +19888,11 @@
         <v>0.375</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="N4" s="1">
         <v>12.7</v>
@@ -19859,7 +19904,7 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="T4" s="1"/>
       <c r="U4" s="1">
@@ -19871,7 +19916,7 @@
       </c>
       <c r="X4" s="1"/>
       <c r="Y4" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1">
@@ -19885,7 +19930,7 @@
         <v>28.574999999999999</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C5" s="1">
         <v>1.125</v>
@@ -19910,11 +19955,11 @@
         <v>0.5</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="N5" s="1">
         <v>15.875</v>
@@ -19936,7 +19981,7 @@
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="Z5" s="1">
         <v>420</v>
@@ -19950,7 +19995,7 @@
         <v>31.75</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C6" s="1">
         <v>1.25</v>
@@ -19975,11 +20020,11 @@
         <v>0.625</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="N6" s="1">
         <v>19.05</v>
@@ -20011,7 +20056,7 @@
         <v>34.924999999999997</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C7" s="1">
         <v>1.375</v>
@@ -20036,11 +20081,11 @@
         <v>0.75</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="N7" s="1">
         <v>22.225000000000001</v>
@@ -20072,7 +20117,7 @@
         <v>38.1</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C8" s="1">
         <v>1.5</v>
@@ -20097,11 +20142,11 @@
         <v>0.875</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="N8" s="1">
         <v>25.4</v>
@@ -20133,7 +20178,7 @@
         <v>44.45</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C9" s="1">
         <v>1.75</v>
@@ -20158,11 +20203,11 @@
         <v>1</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="N9" s="1">
         <v>28.65</v>
@@ -20190,7 +20235,7 @@
         <v>50.8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
@@ -20215,11 +20260,11 @@
         <v>1.25</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="N10" s="1">
         <v>32.26</v>
@@ -20258,7 +20303,7 @@
         <v>1.5</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -20295,7 +20340,7 @@
         <v>1.75</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -20332,7 +20377,7 @@
         <v>2</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -20369,7 +20414,7 @@
         <v>2.25</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -20406,7 +20451,7 @@
         <v>2.5</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -20443,7 +20488,7 @@
         <v>3</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -20480,7 +20525,7 @@
         <v>3.5</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -20517,7 +20562,7 @@
         <v>4</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -26193,15 +26238,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AC200"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="61.58203125" customWidth="1"/>
+    <col min="1" max="1" width="61.625" customWidth="1"/>
     <col min="2" max="2" width="178.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="18">
       <c r="A1" s="20" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="8"/>
@@ -26232,12 +26277,12 @@
       <c r="AB1" s="8"/>
       <c r="AC1" s="8"/>
     </row>
-    <row r="2" spans="1:29" ht="28">
+    <row r="2" spans="1:29" ht="29.25">
       <c r="A2" s="9" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -26267,12 +26312,12 @@
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
     </row>
-    <row r="3" spans="1:29">
+    <row r="3" spans="1:29" ht="15">
       <c r="A3" s="9" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -26302,12 +26347,12 @@
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
     </row>
-    <row r="4" spans="1:29">
+    <row r="4" spans="1:29" ht="15">
       <c r="A4" s="9" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -26337,12 +26382,12 @@
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
     </row>
-    <row r="5" spans="1:29">
+    <row r="5" spans="1:29" ht="15">
       <c r="A5" s="9" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -26372,12 +26417,12 @@
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
     </row>
-    <row r="6" spans="1:29">
+    <row r="6" spans="1:29" ht="15">
       <c r="A6" s="9" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>

--- a/Programacion_conexion_columna_placa_base_AISC.xlsx
+++ b/Programacion_conexion_columna_placa_base_AISC.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\byomayusa\Documents\GitHub\StructureLab_HFS_CNT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\Proyectos python\StructureLab_HFS_CNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638822D9-2A7E-43AE-BE95-3C996B71E505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6000E528-0B93-43B7-A890-C6F82D0931FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DISENO_CONEXION" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="626">
   <si>
     <t>CONEXIÓN COLUMNA - PLACA BASE AXIAL + MOMENTO</t>
   </si>
@@ -1911,6 +1911,9 @@
   </si>
   <si>
     <t>Sobresale pedestal X</t>
+  </si>
+  <si>
+    <t>`454.3</t>
   </si>
 </sst>
 </file>
@@ -2055,6 +2058,18 @@
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2067,20 +2082,8 @@
     <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2368,7 +2371,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L184"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -2380,29 +2383,29 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22.35" customHeight="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:10" ht="22.4" customHeight="1">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
     </row>
     <row r="2" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1"/>
@@ -2415,22 +2418,22 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="13" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -2450,7 +2453,7 @@
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="13" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="4">
@@ -2472,7 +2475,7 @@
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="13" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="4">
@@ -2492,7 +2495,7 @@
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="13" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="4">
@@ -2536,7 +2539,7 @@
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="10">
@@ -2556,7 +2559,7 @@
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="4">
@@ -2576,7 +2579,7 @@
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="10">
@@ -2598,7 +2601,7 @@
       <c r="A13" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="13" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="10">
@@ -2620,7 +2623,7 @@
       <c r="A14" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="13" t="s">
         <v>623</v>
       </c>
       <c r="C14" s="12">
@@ -2638,7 +2641,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2"/>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="13" t="s">
         <v>621</v>
       </c>
       <c r="C15" s="12">
@@ -2654,7 +2657,7 @@
       <c r="A16" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="13" t="s">
         <v>622</v>
       </c>
       <c r="C16" s="10">
@@ -2676,7 +2679,7 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="2"/>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="13" t="s">
         <v>624</v>
       </c>
       <c r="C17" s="10">
@@ -2688,15 +2691,15 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:11" ht="25.5">
+    <row r="18" spans="1:11" ht="25">
       <c r="A18" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="10">
-        <v>430</v>
+      <c r="C18" s="10" t="s">
+        <v>625</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>25</v>
@@ -2714,7 +2717,7 @@
       <c r="A19" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="13" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="10">
@@ -2738,7 +2741,7 @@
       <c r="A20" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="13" t="s">
         <v>38</v>
       </c>
       <c r="C20" s="10">
@@ -2760,7 +2763,7 @@
       <c r="A21" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="13" t="s">
         <v>41</v>
       </c>
       <c r="C21" s="10">
@@ -2784,7 +2787,7 @@
       <c r="A22" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="13" t="s">
         <v>43</v>
       </c>
       <c r="C22" s="10">
@@ -2811,7 +2814,7 @@
       <c r="A23" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="13" t="s">
         <v>47</v>
       </c>
       <c r="C23" s="4" t="s">
@@ -2829,11 +2832,11 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="25.5">
+    <row r="24" spans="1:11" ht="25">
       <c r="A24" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="13" t="s">
         <v>50</v>
       </c>
       <c r="C24" s="4" t="s">
@@ -2857,7 +2860,7 @@
       <c r="A25" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="13" t="s">
         <v>54</v>
       </c>
       <c r="C25" s="4">
@@ -2881,7 +2884,7 @@
       <c r="A26" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="13" t="s">
         <v>56</v>
       </c>
       <c r="C26" s="4">
@@ -2901,7 +2904,7 @@
       <c r="A27" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="13" t="s">
         <v>58</v>
       </c>
       <c r="C27" s="4">
@@ -2923,7 +2926,7 @@
       <c r="A28" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="13" t="s">
         <v>61</v>
       </c>
       <c r="C28" s="4">
@@ -2943,7 +2946,7 @@
       <c r="A29" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="13" t="s">
         <v>63</v>
       </c>
       <c r="C29" s="4">
@@ -2965,7 +2968,7 @@
       <c r="A30" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="13" t="s">
         <v>66</v>
       </c>
       <c r="C30" s="4">
@@ -2987,7 +2990,7 @@
       <c r="A31" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="13" t="s">
         <v>69</v>
       </c>
       <c r="C31" s="4">
@@ -3007,7 +3010,7 @@
       <c r="A32" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="13" t="s">
         <v>71</v>
       </c>
       <c r="C32" s="4">
@@ -3026,22 +3029,22 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="17.649999999999999" customHeight="1">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B34" s="21" t="s">
+      <c r="B34" s="13" t="s">
         <v>76</v>
       </c>
       <c r="C34" s="5">
@@ -3062,7 +3065,7 @@
       <c r="A35" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="13" t="s">
         <v>78</v>
       </c>
       <c r="C35" s="5">
@@ -3083,7 +3086,7 @@
       <c r="A36" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="13" t="s">
         <v>79</v>
       </c>
       <c r="C36" s="5">
@@ -3104,7 +3107,7 @@
       <c r="A37" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="21" t="s">
+      <c r="B37" s="13" t="s">
         <v>80</v>
       </c>
       <c r="C37" s="5">
@@ -3125,7 +3128,7 @@
       <c r="A38" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="13" t="s">
         <v>81</v>
       </c>
       <c r="C38" s="5">
@@ -3146,7 +3149,7 @@
       <c r="A39" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="13" t="s">
         <v>82</v>
       </c>
       <c r="C39" s="5">
@@ -3167,7 +3170,7 @@
       <c r="A40" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="13" t="s">
         <v>83</v>
       </c>
       <c r="C40" s="5">
@@ -3188,7 +3191,7 @@
       <c r="A41" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="13" t="s">
         <v>85</v>
       </c>
       <c r="C41" s="5">
@@ -3209,7 +3212,7 @@
       <c r="A42" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="13" t="s">
         <v>87</v>
       </c>
       <c r="C42" s="5">
@@ -3230,7 +3233,7 @@
       <c r="A43" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="13" t="s">
         <v>89</v>
       </c>
       <c r="C43" s="5">
@@ -3251,7 +3254,7 @@
       <c r="A44" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B44" s="21" t="s">
+      <c r="B44" s="13" t="s">
         <v>91</v>
       </c>
       <c r="C44" s="5">
@@ -3274,7 +3277,7 @@
       <c r="A45" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B45" s="21" t="s">
+      <c r="B45" s="13" t="s">
         <v>94</v>
       </c>
       <c r="C45" s="5">
@@ -3294,22 +3297,22 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="17.649999999999999" customHeight="1">
-      <c r="A46" s="17" t="s">
+      <c r="A46" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="B46" s="17"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B47" s="21" t="s">
+      <c r="B47" s="13" t="s">
         <v>98</v>
       </c>
       <c r="C47" s="4">
@@ -3331,7 +3334,7 @@
       <c r="A48" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B48" s="21" t="s">
+      <c r="B48" s="13" t="s">
         <v>101</v>
       </c>
       <c r="C48" s="4">
@@ -3353,7 +3356,7 @@
       <c r="A49" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B49" s="21" t="s">
+      <c r="B49" s="13" t="s">
         <v>104</v>
       </c>
       <c r="C49" s="4">
@@ -3375,7 +3378,7 @@
       <c r="A50" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B50" s="21" t="s">
+      <c r="B50" s="13" t="s">
         <v>106</v>
       </c>
       <c r="C50" s="4">
@@ -3395,7 +3398,7 @@
       <c r="A51" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B51" s="21" t="s">
+      <c r="B51" s="13" t="s">
         <v>108</v>
       </c>
       <c r="C51" s="4">
@@ -3415,7 +3418,7 @@
       <c r="A52" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B52" s="21" t="s">
+      <c r="B52" s="13" t="s">
         <v>110</v>
       </c>
       <c r="C52" s="4">
@@ -3435,7 +3438,7 @@
       <c r="A53" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B53" s="21" t="s">
+      <c r="B53" s="13" t="s">
         <v>113</v>
       </c>
       <c r="C53" s="5">
@@ -3456,7 +3459,7 @@
       <c r="A54" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B54" s="21" t="s">
+      <c r="B54" s="13" t="s">
         <v>115</v>
       </c>
       <c r="C54" s="5">
@@ -3477,7 +3480,7 @@
       <c r="A55" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B55" s="21" t="s">
+      <c r="B55" s="13" t="s">
         <v>117</v>
       </c>
       <c r="C55" s="5">
@@ -3498,7 +3501,7 @@
       <c r="A56" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B56" s="21" t="s">
+      <c r="B56" s="13" t="s">
         <v>119</v>
       </c>
       <c r="C56" s="5">
@@ -3519,7 +3522,7 @@
       <c r="A57" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B57" s="21" t="s">
+      <c r="B57" s="13" t="s">
         <v>121</v>
       </c>
       <c r="C57" s="5">
@@ -3540,7 +3543,7 @@
       <c r="A58" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B58" s="21" t="s">
+      <c r="B58" s="13" t="s">
         <v>123</v>
       </c>
       <c r="C58" s="5">
@@ -3558,22 +3561,22 @@
       <c r="H58" s="2"/>
     </row>
     <row r="59" spans="1:8" ht="17.649999999999999" customHeight="1">
-      <c r="A59" s="17" t="s">
+      <c r="A59" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="B59" s="17"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="17"/>
-      <c r="F59" s="17"/>
-      <c r="G59" s="17"/>
-      <c r="H59" s="17"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B60" s="21" t="s">
+      <c r="B60" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C60" s="5">
@@ -3594,7 +3597,7 @@
       <c r="A61" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B61" s="21" t="s">
+      <c r="B61" s="13" t="s">
         <v>130</v>
       </c>
       <c r="C61" s="5">
@@ -3615,7 +3618,7 @@
       <c r="A62" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B62" s="21" t="s">
+      <c r="B62" s="13" t="s">
         <v>133</v>
       </c>
       <c r="C62" s="5">
@@ -3636,7 +3639,7 @@
       <c r="A63" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B63" s="21" t="s">
+      <c r="B63" s="13" t="s">
         <v>136</v>
       </c>
       <c r="C63" s="5" t="str">
@@ -3735,7 +3738,7 @@
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
     </row>
-    <row r="68" spans="1:11" ht="25.5">
+    <row r="68" spans="1:11" ht="26">
       <c r="A68" s="2" t="s">
         <v>147</v>
       </c>
@@ -3755,22 +3758,22 @@
       <c r="H68" s="2"/>
     </row>
     <row r="69" spans="1:11" ht="17.649999999999999" customHeight="1">
-      <c r="A69" s="17" t="s">
+      <c r="A69" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="B69" s="17"/>
-      <c r="C69" s="18"/>
-      <c r="D69" s="19"/>
-      <c r="E69" s="17"/>
-      <c r="F69" s="17"/>
-      <c r="G69" s="17"/>
-      <c r="H69" s="17"/>
+      <c r="B69" s="14"/>
+      <c r="C69" s="15"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
+      <c r="H69" s="14"/>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B70" s="21" t="s">
+      <c r="B70" s="13" t="s">
         <v>151</v>
       </c>
       <c r="C70" s="5">
@@ -3791,7 +3794,7 @@
       <c r="A71" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B71" s="21" t="s">
+      <c r="B71" s="13" t="s">
         <v>152</v>
       </c>
       <c r="C71" s="5">
@@ -3812,7 +3815,7 @@
       <c r="A72" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B72" s="21" t="s">
+      <c r="B72" s="13" t="s">
         <v>153</v>
       </c>
       <c r="C72" s="5">
@@ -3833,7 +3836,7 @@
       <c r="A73" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B73" s="21" t="s">
+      <c r="B73" s="13" t="s">
         <v>154</v>
       </c>
       <c r="C73" s="5" t="str">
@@ -3852,7 +3855,7 @@
       <c r="A74" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B74" s="21" t="s">
+      <c r="B74" s="13" t="s">
         <v>156</v>
       </c>
       <c r="C74" s="5">
@@ -3873,7 +3876,7 @@
       <c r="A75" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B75" s="21" t="s">
+      <c r="B75" s="13" t="s">
         <v>159</v>
       </c>
       <c r="C75" s="5">
@@ -3894,7 +3897,7 @@
       <c r="A76" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B76" s="21" t="s">
+      <c r="B76" s="13" t="s">
         <v>162</v>
       </c>
       <c r="C76" s="5">
@@ -3915,7 +3918,7 @@
       <c r="A77" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B77" s="21" t="s">
+      <c r="B77" s="13" t="s">
         <v>164</v>
       </c>
       <c r="C77" s="5" t="str">
@@ -4136,7 +4139,7 @@
       <c r="A87" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B87" s="21" t="s">
+      <c r="B87" s="13" t="s">
         <v>188</v>
       </c>
       <c r="C87" s="4">
@@ -4172,22 +4175,22 @@
       <c r="H88" s="2"/>
     </row>
     <row r="89" spans="1:12" ht="17.649999999999999" customHeight="1">
-      <c r="A89" s="17" t="s">
+      <c r="A89" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="B89" s="17"/>
-      <c r="C89" s="18"/>
-      <c r="D89" s="19"/>
-      <c r="E89" s="17"/>
-      <c r="F89" s="17"/>
-      <c r="G89" s="17"/>
-      <c r="H89" s="17"/>
+      <c r="B89" s="14"/>
+      <c r="C89" s="15"/>
+      <c r="D89" s="16"/>
+      <c r="E89" s="14"/>
+      <c r="F89" s="14"/>
+      <c r="G89" s="14"/>
+      <c r="H89" s="14"/>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B90" s="21" t="s">
+      <c r="B90" s="13" t="s">
         <v>193</v>
       </c>
       <c r="C90" s="4">
@@ -4249,7 +4252,7 @@
       <c r="A93" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B93" s="21" t="s">
+      <c r="B93" s="13" t="s">
         <v>202</v>
       </c>
       <c r="C93" s="4">
@@ -4289,7 +4292,7 @@
       <c r="A95" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B95" s="21" t="s">
+      <c r="B95" s="13" t="s">
         <v>206</v>
       </c>
       <c r="C95" s="4">
@@ -4309,7 +4312,7 @@
       <c r="A96" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B96" s="21" t="s">
+      <c r="B96" s="13" t="s">
         <v>209</v>
       </c>
       <c r="C96" s="4">
@@ -4408,22 +4411,22 @@
       <c r="H100" s="2"/>
     </row>
     <row r="101" spans="1:8" ht="17.649999999999999" customHeight="1">
-      <c r="A101" s="17" t="s">
+      <c r="A101" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="B101" s="17"/>
-      <c r="C101" s="18"/>
-      <c r="D101" s="19"/>
-      <c r="E101" s="17"/>
-      <c r="F101" s="17"/>
-      <c r="G101" s="17"/>
-      <c r="H101" s="17"/>
+      <c r="B101" s="14"/>
+      <c r="C101" s="15"/>
+      <c r="D101" s="16"/>
+      <c r="E101" s="14"/>
+      <c r="F101" s="14"/>
+      <c r="G101" s="14"/>
+      <c r="H101" s="14"/>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B102" s="21" t="s">
+      <c r="B102" s="13" t="s">
         <v>221</v>
       </c>
       <c r="C102" s="5">
@@ -4444,7 +4447,7 @@
       <c r="A103" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B103" s="21" t="s">
+      <c r="B103" s="13" t="s">
         <v>223</v>
       </c>
       <c r="C103" s="5">
@@ -4489,9 +4492,9 @@
       <c r="B105" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C105" s="5">
+      <c r="C105" s="5" t="e">
         <f>1.5*$C$18</f>
-        <v>645</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D105" s="7" t="s">
         <v>25</v>
@@ -4510,9 +4513,9 @@
       <c r="B106" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C106" s="5">
+      <c r="C106" s="5" t="e">
         <f>MAX(($C$105-$C$104)/2,0)</f>
-        <v>272.5</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D106" s="7" t="s">
         <v>25</v>
@@ -4531,9 +4534,9 @@
       <c r="B107" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C107" s="5">
+      <c r="C107" s="5" t="e">
         <f>($C$104+$C$105)*$C$103</f>
-        <v>633250</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D107" s="7" t="s">
         <v>160</v>
@@ -4552,9 +4555,9 @@
       <c r="B108" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C108" s="5">
+      <c r="C108" s="5" t="e">
         <f>9*$C$18^2</f>
-        <v>1664100</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D108" s="7" t="s">
         <v>160</v>
@@ -4573,9 +4576,9 @@
       <c r="B109" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C109" s="5">
+      <c r="C109" s="5" t="e">
         <f>1/(1+2*$C$106/(3*$C$18))</f>
-        <v>0.70299727520435973</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D109" s="7" t="s">
         <v>13</v>
@@ -4594,9 +4597,9 @@
       <c r="B110" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C110" s="5">
+      <c r="C110" s="5" t="e">
         <f>IF($C$104&gt;=$C$105,1,0.7+0.3*$C$104/$C$105)</f>
-        <v>0.74651162790697667</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D110" s="7" t="s">
         <v>13</v>
@@ -4699,9 +4702,9 @@
       <c r="B115" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C115" s="5">
+      <c r="C115" s="5" t="e">
         <f>$C$114*$C$113*SQRT($C$10)*$C$18^1.5/1000</f>
-        <v>471.82581531747456</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D115" s="7" t="s">
         <v>99</v>
@@ -4720,9 +4723,9 @@
       <c r="B116" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C116" s="5">
+      <c r="C116" s="5" t="e">
         <f>$C$107/$C$108*$C$109*$C$110*$C$111*$C$112*$C$115</f>
-        <v>94.22533614260189</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D116" s="7" t="s">
         <v>99</v>
@@ -4741,9 +4744,9 @@
       <c r="B117" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C117" s="5">
+      <c r="C117" s="5" t="e">
         <f>$C$94*$C$116</f>
-        <v>70.66900210695141</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D117" s="7" t="s">
         <v>99</v>
@@ -4755,16 +4758,16 @@
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
     </row>
-    <row r="118" spans="1:11" ht="38.25">
+    <row r="118" spans="1:11" ht="39">
       <c r="A118" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C118" s="5" t="str">
+      <c r="C118" s="5" t="e">
         <f>IF($C$117&gt;=$C$80,"CUMPLE","NO CUMPLE - USAR REFUERZO SUPLEMENTARIO")</f>
-        <v>NO CUMPLE - USAR REFUERZO SUPLEMENTARIO</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D118" s="7"/>
       <c r="E118" s="2" t="s">
@@ -4782,7 +4785,7 @@
       <c r="A119" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B119" s="21" t="s">
+      <c r="B119" s="13" t="s">
         <v>260</v>
       </c>
       <c r="C119" s="4">
@@ -4802,7 +4805,7 @@
       <c r="A120" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B120" s="21" t="s">
+      <c r="B120" s="13" t="s">
         <v>262</v>
       </c>
       <c r="C120" s="4">
@@ -4822,7 +4825,7 @@
       <c r="A121" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B121" s="21" t="s">
+      <c r="B121" s="13" t="s">
         <v>264</v>
       </c>
       <c r="C121" s="4" t="s">
@@ -4899,7 +4902,7 @@
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
     </row>
-    <row r="125" spans="1:11" ht="25.5">
+    <row r="125" spans="1:11" ht="25">
       <c r="A125" s="2" t="s">
         <v>267</v>
       </c>
@@ -4965,16 +4968,16 @@
       <c r="H127" s="2"/>
     </row>
     <row r="128" spans="1:11" ht="17.649999999999999" customHeight="1">
-      <c r="A128" s="17" t="s">
+      <c r="A128" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="B128" s="17"/>
-      <c r="C128" s="18"/>
-      <c r="D128" s="19"/>
-      <c r="E128" s="17"/>
-      <c r="F128" s="17"/>
-      <c r="G128" s="17"/>
-      <c r="H128" s="17"/>
+      <c r="B128" s="14"/>
+      <c r="C128" s="15"/>
+      <c r="D128" s="16"/>
+      <c r="E128" s="14"/>
+      <c r="F128" s="14"/>
+      <c r="G128" s="14"/>
+      <c r="H128" s="14"/>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="2" t="s">
@@ -5348,7 +5351,7 @@
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
     </row>
-    <row r="147" spans="1:8" ht="38.25">
+    <row r="147" spans="1:8" ht="37.5">
       <c r="A147" s="2" t="s">
         <v>147</v>
       </c>
@@ -5410,16 +5413,16 @@
       <c r="H149" s="2"/>
     </row>
     <row r="150" spans="1:8" ht="17.649999999999999" customHeight="1">
-      <c r="A150" s="17" t="s">
+      <c r="A150" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="B150" s="17"/>
-      <c r="C150" s="18"/>
-      <c r="D150" s="19"/>
-      <c r="E150" s="17"/>
-      <c r="F150" s="17"/>
-      <c r="G150" s="17"/>
-      <c r="H150" s="17"/>
+      <c r="B150" s="14"/>
+      <c r="C150" s="15"/>
+      <c r="D150" s="16"/>
+      <c r="E150" s="14"/>
+      <c r="F150" s="14"/>
+      <c r="G150" s="14"/>
+      <c r="H150" s="14"/>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="2" t="s">
@@ -5467,7 +5470,7 @@
       <c r="A153" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B153" s="21" t="s">
+      <c r="B153" s="13" t="s">
         <v>336</v>
       </c>
       <c r="C153" s="4">
@@ -5921,16 +5924,16 @@
       <c r="H174" s="2"/>
     </row>
     <row r="175" spans="1:8" ht="17.649999999999999" customHeight="1">
-      <c r="A175" s="17" t="s">
+      <c r="A175" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="B175" s="17"/>
-      <c r="C175" s="18"/>
-      <c r="D175" s="19"/>
-      <c r="E175" s="17"/>
-      <c r="F175" s="17"/>
-      <c r="G175" s="17"/>
-      <c r="H175" s="17"/>
+      <c r="B175" s="14"/>
+      <c r="C175" s="15"/>
+      <c r="D175" s="16"/>
+      <c r="E175" s="14"/>
+      <c r="F175" s="14"/>
+      <c r="G175" s="14"/>
+      <c r="H175" s="14"/>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="2" t="s">
@@ -5970,16 +5973,16 @@
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
     </row>
-    <row r="178" spans="1:8" ht="38.25">
+    <row r="178" spans="1:8" ht="39">
       <c r="A178" s="2" t="s">
         <v>387</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C178" s="5" t="str">
+      <c r="C178" s="5" t="e">
         <f>IF(LEFT($C$118,6)="CUMPLE","CUMPLE POR CONCRETO","CUMPLE CON REFUERZO SUPLEMENTARIO")</f>
-        <v>CUMPLE CON REFUERZO SUPLEMENTARIO</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D178" s="7"/>
       <c r="E178" s="2" t="s">
@@ -5989,7 +5992,7 @@
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
     </row>
-    <row r="179" spans="1:8" ht="25.5">
+    <row r="179" spans="1:8" ht="26">
       <c r="A179" s="2" t="s">
         <v>387</v>
       </c>
@@ -6084,16 +6087,16 @@
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
     </row>
-    <row r="184" spans="1:8" ht="25.5">
+    <row r="184" spans="1:8" ht="26">
       <c r="A184" s="2" t="s">
         <v>387</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="C184" s="5" t="str">
+      <c r="C184" s="5" t="e">
         <f>IF(AND(LEFT($C$176,6)="CUMPLE",LEFT($C$177,6)="CUMPLE",LEFT($C$178,6)="CUMPLE",LEFT($C$179,6)="CUMPLE",$C$180&lt;&gt;"NO CUMPLE",LEFT($C$181,6)="CUMPLE",LEFT($C$182,6)="CUMPLE",LEFT($C$183,6)="CUMPLE"),"CUMPLE - REVISAR DETALLE FINAL","NO CUMPLE / AJUSTAR VARIABLES")</f>
-        <v>CUMPLE - REVISAR DETALLE FINAL</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D184" s="7"/>
       <c r="E184" s="2" t="s">
@@ -6105,6 +6108,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A128:H128"/>
     <mergeCell ref="A150:H150"/>
     <mergeCell ref="A175:H175"/>
     <mergeCell ref="A46:H46"/>
@@ -6112,11 +6120,6 @@
     <mergeCell ref="A69:H69"/>
     <mergeCell ref="A89:H89"/>
     <mergeCell ref="A101:H101"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A128:H128"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C184">
     <cfRule type="expression" dxfId="3" priority="1">
@@ -6193,12 +6196,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AC200"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="29" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="15">
+    <row r="1" spans="1:29">
       <c r="A1" s="8" t="s">
         <v>406</v>
       </c>
@@ -19621,31 +19624,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AC200"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="6.625" customWidth="1"/>
+    <col min="1" max="1" width="6.58203125" customWidth="1"/>
     <col min="2" max="2" width="6.75" customWidth="1"/>
-    <col min="3" max="3" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="6.83203125" customWidth="1"/>
     <col min="4" max="4" width="11.25" customWidth="1"/>
     <col min="5" max="5" width="14.25" customWidth="1"/>
-    <col min="6" max="6" width="10.875" customWidth="1"/>
-    <col min="7" max="7" width="10.125" customWidth="1"/>
-    <col min="9" max="9" width="5.375" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.08203125" customWidth="1"/>
+    <col min="9" max="9" width="5.33203125" customWidth="1"/>
     <col min="10" max="10" width="7.25" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
     <col min="13" max="13" width="4.25" customWidth="1"/>
     <col min="14" max="14" width="6.75" customWidth="1"/>
-    <col min="15" max="15" width="10.375" customWidth="1"/>
-    <col min="17" max="17" width="4.625" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" customWidth="1"/>
+    <col min="17" max="17" width="4.58203125" customWidth="1"/>
     <col min="19" max="19" width="9.25" customWidth="1"/>
-    <col min="21" max="21" width="16.375" customWidth="1"/>
+    <col min="21" max="21" width="16.33203125" customWidth="1"/>
     <col min="23" max="23" width="18.75" customWidth="1"/>
-    <col min="25" max="25" width="13.875" customWidth="1"/>
-    <col min="26" max="26" width="5.875" customWidth="1"/>
-    <col min="27" max="27" width="6.125" customWidth="1"/>
+    <col min="25" max="25" width="13.83203125" customWidth="1"/>
+    <col min="26" max="26" width="5.83203125" customWidth="1"/>
+    <col min="27" max="27" width="6.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="30">
+    <row r="1" spans="1:29" ht="28">
       <c r="A1" s="8" t="s">
         <v>559</v>
       </c>
@@ -19716,7 +19719,7 @@
       <c r="AB1" s="8"/>
       <c r="AC1" s="8"/>
     </row>
-    <row r="2" spans="1:29" ht="28.5">
+    <row r="2" spans="1:29" ht="28">
       <c r="A2" s="1">
         <v>19.05</v>
       </c>
@@ -19787,7 +19790,7 @@
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
     </row>
-    <row r="3" spans="1:29" ht="28.5">
+    <row r="3" spans="1:29" ht="28">
       <c r="A3" s="1">
         <v>22.225000000000001</v>
       </c>
@@ -26238,17 +26241,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AC200"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="61.625" customWidth="1"/>
+    <col min="1" max="1" width="61.58203125" customWidth="1"/>
     <col min="2" max="2" width="178.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="18">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>609</v>
       </c>
-      <c r="B1" s="20"/>
+      <c r="B1" s="21"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
@@ -26277,7 +26280,7 @@
       <c r="AB1" s="8"/>
       <c r="AC1" s="8"/>
     </row>
-    <row r="2" spans="1:29" ht="29.25">
+    <row r="2" spans="1:29" ht="28">
       <c r="A2" s="9" t="s">
         <v>610</v>
       </c>
@@ -26312,7 +26315,7 @@
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
     </row>
-    <row r="3" spans="1:29" ht="15">
+    <row r="3" spans="1:29">
       <c r="A3" s="9" t="s">
         <v>612</v>
       </c>
@@ -26347,7 +26350,7 @@
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
     </row>
-    <row r="4" spans="1:29" ht="15">
+    <row r="4" spans="1:29">
       <c r="A4" s="9" t="s">
         <v>614</v>
       </c>
@@ -26382,7 +26385,7 @@
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="15">
+    <row r="5" spans="1:29">
       <c r="A5" s="9" t="s">
         <v>616</v>
       </c>
@@ -26417,7 +26420,7 @@
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
     </row>
-    <row r="6" spans="1:29" ht="15">
+    <row r="6" spans="1:29">
       <c r="A6" s="9" t="s">
         <v>618</v>
       </c>

--- a/Programacion_conexion_columna_placa_base_AISC.xlsx
+++ b/Programacion_conexion_columna_placa_base_AISC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\Proyectos python\StructureLab_HFS_CNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6000E528-0B93-43B7-A890-C6F82D0931FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{04C08C34-FC79-4B34-9B78-BC934A530288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DISENO_CONEXION" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="626">
   <si>
     <t>CONEXIÓN COLUMNA - PLACA BASE AXIAL + MOMENTO</t>
   </si>
@@ -1913,7 +1911,7 @@
     <t>Sobresale pedestal X</t>
   </si>
   <si>
-    <t>`454.3</t>
+    <t>C23</t>
   </si>
 </sst>
 </file>
@@ -2022,7 +2020,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2061,15 +2059,7 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2080,6 +2070,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2371,7 +2370,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L184"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -2383,31 +2382,31 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22.4" customHeight="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:11" ht="22.4" customHeight="1">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-    </row>
-    <row r="2" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A2" s="19" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" spans="1:11" ht="17.75" customHeight="1">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="B2" s="17"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="3"/>
@@ -2417,19 +2416,19 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A4" s="14" t="s">
+    <row r="4" spans="1:11" ht="17.75" customHeight="1">
+      <c r="A4" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="B4" s="19"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -2449,7 +2448,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -2471,7 +2470,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -2491,7 +2490,7 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:11">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -2513,7 +2512,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:11">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -2535,7 +2534,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:11">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -2554,8 +2553,12 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="K10" s="14">
+        <f>C14+C16</f>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -2575,7 +2578,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:11">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
@@ -2597,7 +2600,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:11">
       <c r="A13" s="2" t="s">
         <v>3</v>
       </c>
@@ -2619,7 +2622,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:11">
       <c r="A14" s="2" t="s">
         <v>3</v>
       </c>
@@ -2639,7 +2642,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:11">
       <c r="A15" s="2"/>
       <c r="B15" s="13" t="s">
         <v>621</v>
@@ -2653,7 +2656,7 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:11">
       <c r="A16" s="2" t="s">
         <v>3</v>
       </c>
@@ -2698,8 +2701,8 @@
       <c r="B18" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>625</v>
+      <c r="C18" s="10">
+        <v>450</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>25</v>
@@ -2941,6 +2944,10 @@
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
+      <c r="J28">
+        <f>382.86+50</f>
+        <v>432.86</v>
+      </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2" t="s">
@@ -3028,17 +3035,17 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="17.649999999999999" customHeight="1">
-      <c r="A33" s="14" t="s">
+    <row r="33" spans="1:8" ht="17.75" customHeight="1">
+      <c r="A33" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="2" t="s">
@@ -3296,17 +3303,17 @@
         <v>93</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="17.649999999999999" customHeight="1">
-      <c r="A46" s="14" t="s">
+    <row r="46" spans="1:8" ht="17.75" customHeight="1">
+      <c r="A46" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="B46" s="14"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="2" t="s">
@@ -3390,7 +3397,9 @@
       <c r="E50" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F50" s="2"/>
+      <c r="F50" s="2" t="s">
+        <v>625</v>
+      </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
     </row>
@@ -3410,7 +3419,9 @@
       <c r="E51" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F51" s="2"/>
+      <c r="F51" s="2" t="s">
+        <v>625</v>
+      </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
     </row>
@@ -3430,7 +3441,9 @@
       <c r="E52" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F52" s="2"/>
+      <c r="F52" s="2" t="s">
+        <v>625</v>
+      </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
     </row>
@@ -3560,17 +3573,17 @@
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
     </row>
-    <row r="59" spans="1:8" ht="17.649999999999999" customHeight="1">
-      <c r="A59" s="14" t="s">
+    <row r="59" spans="1:8" ht="17.75" customHeight="1">
+      <c r="A59" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="B59" s="14"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19"/>
+      <c r="H59" s="19"/>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="2" t="s">
@@ -3757,17 +3770,17 @@
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
     </row>
-    <row r="69" spans="1:11" ht="17.649999999999999" customHeight="1">
-      <c r="A69" s="14" t="s">
+    <row r="69" spans="1:11" ht="17.75" customHeight="1">
+      <c r="A69" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="B69" s="14"/>
-      <c r="C69" s="15"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
+      <c r="B69" s="19"/>
+      <c r="C69" s="20"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="2" t="s">
@@ -3937,7 +3950,7 @@
       <c r="A78" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="13" t="s">
         <v>166</v>
       </c>
       <c r="C78" s="5">
@@ -3958,7 +3971,7 @@
       <c r="A79" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="13" t="s">
         <v>168</v>
       </c>
       <c r="C79" s="5">
@@ -3984,7 +3997,7 @@
       <c r="A80" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="13" t="s">
         <v>172</v>
       </c>
       <c r="C80" s="5">
@@ -4009,7 +4022,7 @@
       <c r="A81" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="13" t="s">
         <v>175</v>
       </c>
       <c r="C81" s="5">
@@ -4030,7 +4043,7 @@
       <c r="A82" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="13" t="s">
         <v>177</v>
       </c>
       <c r="C82" s="5">
@@ -4051,7 +4064,7 @@
       <c r="A83" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="13" t="s">
         <v>179</v>
       </c>
       <c r="C83" s="5">
@@ -4076,7 +4089,7 @@
       <c r="A84" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B84" s="13" t="s">
         <v>182</v>
       </c>
       <c r="C84" s="5">
@@ -4097,7 +4110,7 @@
       <c r="A85" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B85" s="13" t="s">
         <v>184</v>
       </c>
       <c r="C85" s="5">
@@ -4118,7 +4131,7 @@
       <c r="A86" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B86" s="13" t="s">
         <v>186</v>
       </c>
       <c r="C86" s="5">
@@ -4174,17 +4187,17 @@
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
     </row>
-    <row r="89" spans="1:12" ht="17.649999999999999" customHeight="1">
-      <c r="A89" s="14" t="s">
+    <row r="89" spans="1:12" ht="17.75" customHeight="1">
+      <c r="A89" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="B89" s="14"/>
-      <c r="C89" s="15"/>
-      <c r="D89" s="16"/>
-      <c r="E89" s="14"/>
-      <c r="F89" s="14"/>
-      <c r="G89" s="14"/>
-      <c r="H89" s="14"/>
+      <c r="B89" s="19"/>
+      <c r="C89" s="20"/>
+      <c r="D89" s="21"/>
+      <c r="E89" s="19"/>
+      <c r="F89" s="19"/>
+      <c r="G89" s="19"/>
+      <c r="H89" s="19"/>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" s="2" t="s">
@@ -4210,7 +4223,7 @@
       <c r="A91" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B91" s="13" t="s">
         <v>196</v>
       </c>
       <c r="C91" s="5">
@@ -4231,7 +4244,7 @@
       <c r="A92" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="13" t="s">
         <v>199</v>
       </c>
       <c r="C92" s="5">
@@ -4272,7 +4285,7 @@
       <c r="A94" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B94" s="13" t="s">
         <v>204</v>
       </c>
       <c r="C94" s="4">
@@ -4328,11 +4341,11 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:12">
       <c r="A97" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B97" s="13" t="s">
         <v>211</v>
       </c>
       <c r="C97" s="5">
@@ -4345,15 +4358,18 @@
       <c r="E97" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F97" s="2"/>
+      <c r="F97" s="2">
+        <f>C80/C99</f>
+        <v>0.96294826253234966</v>
+      </c>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:12">
       <c r="A98" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="B98" s="13" t="s">
         <v>213</v>
       </c>
       <c r="C98" s="5">
@@ -4370,11 +4386,11 @@
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:12">
       <c r="A99" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="B99" s="13" t="s">
         <v>215</v>
       </c>
       <c r="C99" s="5">
@@ -4391,11 +4407,11 @@
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:12">
       <c r="A100" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B100" s="13" t="s">
         <v>217</v>
       </c>
       <c r="C100" s="5" t="str">
@@ -4410,19 +4426,19 @@
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
     </row>
-    <row r="101" spans="1:8" ht="17.649999999999999" customHeight="1">
-      <c r="A101" s="14" t="s">
+    <row r="101" spans="1:12" ht="17.75" customHeight="1">
+      <c r="A101" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="B101" s="14"/>
-      <c r="C101" s="15"/>
-      <c r="D101" s="16"/>
-      <c r="E101" s="14"/>
-      <c r="F101" s="14"/>
-      <c r="G101" s="14"/>
-      <c r="H101" s="14"/>
-    </row>
-    <row r="102" spans="1:8">
+      <c r="B101" s="19"/>
+      <c r="C101" s="20"/>
+      <c r="D101" s="21"/>
+      <c r="E101" s="19"/>
+      <c r="F101" s="19"/>
+      <c r="G101" s="19"/>
+      <c r="H101" s="19"/>
+    </row>
+    <row r="102" spans="1:12">
       <c r="A102" s="2" t="s">
         <v>220</v>
       </c>
@@ -4443,7 +4459,7 @@
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:12">
       <c r="A103" s="2" t="s">
         <v>220</v>
       </c>
@@ -4464,16 +4480,16 @@
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:12">
       <c r="A104" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="B104" s="13" t="s">
         <v>225</v>
       </c>
       <c r="C104" s="5">
-        <f>$C$15+$C$16</f>
-        <v>100</v>
+        <f>MIN(C14+C16,$C$15+$C$17)</f>
+        <v>125</v>
       </c>
       <c r="D104" s="7" t="s">
         <v>25</v>
@@ -4485,16 +4501,16 @@
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:12">
       <c r="A105" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="B105" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="C105" s="5" t="e">
+      <c r="C105" s="5">
         <f>1.5*$C$18</f>
-        <v>#VALUE!</v>
+        <v>675</v>
       </c>
       <c r="D105" s="7" t="s">
         <v>25</v>
@@ -4506,16 +4522,16 @@
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:12">
       <c r="A106" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="B106" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="C106" s="5" t="e">
+      <c r="C106" s="5">
         <f>MAX(($C$105-$C$104)/2,0)</f>
-        <v>#VALUE!</v>
+        <v>275</v>
       </c>
       <c r="D106" s="7" t="s">
         <v>25</v>
@@ -4527,16 +4543,16 @@
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:12">
       <c r="A107" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="B107" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="C107" s="5" t="e">
+      <c r="C107" s="5">
         <f>($C$104+$C$105)*$C$103</f>
-        <v>#VALUE!</v>
+        <v>680000</v>
       </c>
       <c r="D107" s="7" t="s">
         <v>160</v>
@@ -4548,16 +4564,16 @@
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:12">
       <c r="A108" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="B108" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="C108" s="5" t="e">
+      <c r="C108" s="5">
         <f>9*$C$18^2</f>
-        <v>#VALUE!</v>
+        <v>1822500</v>
       </c>
       <c r="D108" s="7" t="s">
         <v>160</v>
@@ -4569,16 +4585,16 @@
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:12">
       <c r="A109" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B109" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="C109" s="5" t="e">
+      <c r="C109" s="5">
         <f>1/(1+2*$C$106/(3*$C$18))</f>
-        <v>#VALUE!</v>
+        <v>0.71052631578947367</v>
       </c>
       <c r="D109" s="7" t="s">
         <v>13</v>
@@ -4590,16 +4606,16 @@
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:12">
       <c r="A110" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B110" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="C110" s="5" t="e">
+      <c r="C110" s="5">
         <f>IF($C$104&gt;=$C$105,1,0.7+0.3*$C$104/$C$105)</f>
-        <v>#VALUE!</v>
+        <v>0.75555555555555554</v>
       </c>
       <c r="D110" s="7" t="s">
         <v>13</v>
@@ -4610,12 +4626,16 @@
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
-    </row>
-    <row r="111" spans="1:8">
+      <c r="L110">
+        <f>1.4*8*28*C31*C31/1000</f>
+        <v>2540.1599999999994</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12">
       <c r="A111" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B111" s="13" t="s">
         <v>241</v>
       </c>
       <c r="C111" s="4">
@@ -4633,11 +4653,11 @@
         <v>243</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:12">
       <c r="A112" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B112" s="13" t="s">
         <v>244</v>
       </c>
       <c r="C112" s="4">
@@ -4659,7 +4679,7 @@
       <c r="A113" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="B113" s="13" t="s">
         <v>247</v>
       </c>
       <c r="C113" s="4">
@@ -4679,7 +4699,7 @@
       <c r="A114" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="B114" s="13" t="s">
         <v>249</v>
       </c>
       <c r="C114" s="4">
@@ -4699,12 +4719,12 @@
       <c r="A115" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B115" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="C115" s="5" t="e">
+      <c r="C115" s="5">
         <f>$C$114*$C$113*SQRT($C$10)*$C$18^1.5/1000</f>
-        <v>#VALUE!</v>
+        <v>505.12374721448242</v>
       </c>
       <c r="D115" s="7" t="s">
         <v>99</v>
@@ -4720,12 +4740,12 @@
       <c r="A116" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B116" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="C116" s="5" t="e">
+      <c r="C116" s="5">
         <f>$C$107/$C$108*$C$109*$C$110*$C$111*$C$112*$C$115</f>
-        <v>#VALUE!</v>
+        <v>101.17791670434337</v>
       </c>
       <c r="D116" s="7" t="s">
         <v>99</v>
@@ -4741,12 +4761,12 @@
       <c r="A117" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="B117" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="C117" s="5" t="e">
+      <c r="C117" s="5">
         <f>$C$94*$C$116</f>
-        <v>#VALUE!</v>
+        <v>75.883437528257531</v>
       </c>
       <c r="D117" s="7" t="s">
         <v>99</v>
@@ -4762,12 +4782,12 @@
       <c r="A118" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="B118" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="C118" s="5" t="e">
+      <c r="C118" s="5" t="str">
         <f>IF($C$117&gt;=$C$80,"CUMPLE","NO CUMPLE - USAR REFUERZO SUPLEMENTARIO")</f>
-        <v>#VALUE!</v>
+        <v>NO CUMPLE - USAR REFUERZO SUPLEMENTARIO</v>
       </c>
       <c r="D118" s="7"/>
       <c r="E118" s="2" t="s">
@@ -4880,6 +4900,10 @@
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
+      <c r="K123">
+        <f>(C12-2*50-4*9.5-9*25.4)/8</f>
+        <v>41.674999999999997</v>
+      </c>
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="2" t="s">
@@ -4967,17 +4991,17 @@
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
     </row>
-    <row r="128" spans="1:11" ht="17.649999999999999" customHeight="1">
-      <c r="A128" s="14" t="s">
+    <row r="128" spans="1:11" ht="17.75" customHeight="1">
+      <c r="A128" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="B128" s="14"/>
-      <c r="C128" s="15"/>
-      <c r="D128" s="16"/>
-      <c r="E128" s="14"/>
-      <c r="F128" s="14"/>
-      <c r="G128" s="14"/>
-      <c r="H128" s="14"/>
+      <c r="B128" s="19"/>
+      <c r="C128" s="20"/>
+      <c r="D128" s="21"/>
+      <c r="E128" s="19"/>
+      <c r="F128" s="19"/>
+      <c r="G128" s="19"/>
+      <c r="H128" s="19"/>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="2" t="s">
@@ -5412,17 +5436,17 @@
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
     </row>
-    <row r="150" spans="1:8" ht="17.649999999999999" customHeight="1">
-      <c r="A150" s="14" t="s">
+    <row r="150" spans="1:8" ht="17.75" customHeight="1">
+      <c r="A150" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="B150" s="14"/>
-      <c r="C150" s="15"/>
-      <c r="D150" s="16"/>
-      <c r="E150" s="14"/>
-      <c r="F150" s="14"/>
-      <c r="G150" s="14"/>
-      <c r="H150" s="14"/>
+      <c r="B150" s="19"/>
+      <c r="C150" s="20"/>
+      <c r="D150" s="21"/>
+      <c r="E150" s="19"/>
+      <c r="F150" s="19"/>
+      <c r="G150" s="19"/>
+      <c r="H150" s="19"/>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="2" t="s">
@@ -5923,17 +5947,17 @@
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
     </row>
-    <row r="175" spans="1:8" ht="17.649999999999999" customHeight="1">
-      <c r="A175" s="14" t="s">
+    <row r="175" spans="1:8" ht="17.75" customHeight="1">
+      <c r="A175" s="19" t="s">
         <v>386</v>
       </c>
-      <c r="B175" s="14"/>
-      <c r="C175" s="15"/>
-      <c r="D175" s="16"/>
-      <c r="E175" s="14"/>
-      <c r="F175" s="14"/>
-      <c r="G175" s="14"/>
-      <c r="H175" s="14"/>
+      <c r="B175" s="19"/>
+      <c r="C175" s="20"/>
+      <c r="D175" s="21"/>
+      <c r="E175" s="19"/>
+      <c r="F175" s="19"/>
+      <c r="G175" s="19"/>
+      <c r="H175" s="19"/>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="2" t="s">
@@ -5980,9 +6004,9 @@
       <c r="B178" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C178" s="5" t="e">
+      <c r="C178" s="5" t="str">
         <f>IF(LEFT($C$118,6)="CUMPLE","CUMPLE POR CONCRETO","CUMPLE CON REFUERZO SUPLEMENTARIO")</f>
-        <v>#VALUE!</v>
+        <v>CUMPLE CON REFUERZO SUPLEMENTARIO</v>
       </c>
       <c r="D178" s="7"/>
       <c r="E178" s="2" t="s">
@@ -6094,9 +6118,9 @@
       <c r="B184" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="C184" s="5" t="e">
+      <c r="C184" s="5" t="str">
         <f>IF(AND(LEFT($C$176,6)="CUMPLE",LEFT($C$177,6)="CUMPLE",LEFT($C$178,6)="CUMPLE",LEFT($C$179,6)="CUMPLE",$C$180&lt;&gt;"NO CUMPLE",LEFT($C$181,6)="CUMPLE",LEFT($C$182,6)="CUMPLE",LEFT($C$183,6)="CUMPLE"),"CUMPLE - REVISAR DETALLE FINAL","NO CUMPLE / AJUSTAR VARIABLES")</f>
-        <v>#VALUE!</v>
+        <v>CUMPLE - REVISAR DETALLE FINAL</v>
       </c>
       <c r="D184" s="7"/>
       <c r="E184" s="2" t="s">
@@ -6108,11 +6132,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A128:H128"/>
     <mergeCell ref="A150:H150"/>
     <mergeCell ref="A175:H175"/>
     <mergeCell ref="A46:H46"/>
@@ -6120,6 +6139,11 @@
     <mergeCell ref="A69:H69"/>
     <mergeCell ref="A89:H89"/>
     <mergeCell ref="A101:H101"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A128:H128"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C184">
     <cfRule type="expression" dxfId="3" priority="1">
@@ -6135,10 +6159,13 @@
       <formula>ISNUMBER(SEARCH("REVISAR",C1))</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="C30" xr:uid="{F6E6E482-2CFA-40AD-99BC-04E46663BB15}"/>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="8">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>PERFILES!$B$3:$B$125</xm:f>
@@ -6185,7 +6212,7 @@
           <x14:formula1>
             <xm:f>CATALOGOS!$W$2:$W$8</xm:f>
           </x14:formula1>
-          <xm:sqref>C153 C30</xm:sqref>
+          <xm:sqref>C153</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6196,7 +6223,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AC200"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="29" width="15" customWidth="1"/>
   </cols>
@@ -19624,27 +19651,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AC200"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="6.58203125" customWidth="1"/>
-    <col min="2" max="2" width="6.75" customWidth="1"/>
-    <col min="3" max="3" width="6.83203125" customWidth="1"/>
-    <col min="4" max="4" width="11.25" customWidth="1"/>
-    <col min="5" max="5" width="14.25" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="6.6640625" customWidth="1"/>
+    <col min="3" max="3" width="6.9140625" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" customWidth="1"/>
+    <col min="6" max="6" width="10.9140625" customWidth="1"/>
     <col min="7" max="7" width="10.08203125" customWidth="1"/>
-    <col min="9" max="9" width="5.33203125" customWidth="1"/>
-    <col min="10" max="10" width="7.25" customWidth="1"/>
+    <col min="9" max="9" width="5.4140625" customWidth="1"/>
+    <col min="10" max="10" width="7.1640625" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="13" max="13" width="4.25" customWidth="1"/>
-    <col min="14" max="14" width="6.75" customWidth="1"/>
-    <col min="15" max="15" width="10.33203125" customWidth="1"/>
+    <col min="13" max="13" width="4.1640625" customWidth="1"/>
+    <col min="14" max="14" width="6.6640625" customWidth="1"/>
+    <col min="15" max="15" width="10.4140625" customWidth="1"/>
     <col min="17" max="17" width="4.58203125" customWidth="1"/>
-    <col min="19" max="19" width="9.25" customWidth="1"/>
-    <col min="21" max="21" width="16.33203125" customWidth="1"/>
-    <col min="23" max="23" width="18.75" customWidth="1"/>
-    <col min="25" max="25" width="13.83203125" customWidth="1"/>
-    <col min="26" max="26" width="5.83203125" customWidth="1"/>
+    <col min="19" max="19" width="9.1640625" customWidth="1"/>
+    <col min="21" max="21" width="16.4140625" customWidth="1"/>
+    <col min="23" max="23" width="18.6640625" customWidth="1"/>
+    <col min="25" max="25" width="13.9140625" customWidth="1"/>
+    <col min="26" max="26" width="5.9140625" customWidth="1"/>
     <col min="27" max="27" width="6.08203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -26241,17 +26268,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AC200"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="61.58203125" customWidth="1"/>
-    <col min="2" max="2" width="178.75" customWidth="1"/>
+    <col min="2" max="2" width="178.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="18">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>609</v>
       </c>
-      <c r="B1" s="21"/>
+      <c r="B1" s="22"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>

--- a/Programacion_conexion_columna_placa_base_AISC.xlsx
+++ b/Programacion_conexion_columna_placa_base_AISC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\Proyectos python\StructureLab_HFS_CNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04C08C34-FC79-4B34-9B78-BC934A530288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0933BE2C-31EC-4277-825D-94A906C1BD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DISENO_CONEXION" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="631">
   <si>
     <t>CONEXIÓN COLUMNA - PLACA BASE AXIAL + MOMENTO</t>
   </si>
@@ -1912,6 +1912,21 @@
   </si>
   <si>
     <t>C23</t>
+  </si>
+  <si>
+    <t>Np</t>
+  </si>
+  <si>
+    <t>Abrg</t>
+  </si>
+  <si>
+    <t>ca1</t>
+  </si>
+  <si>
+    <t>ca2</t>
+  </si>
+  <si>
+    <t>ca2/ca1</t>
   </si>
 </sst>
 </file>
@@ -2020,7 +2035,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2083,6 +2098,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4603,7 +4621,10 @@
         <v>238</v>
       </c>
       <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
+      <c r="G109" s="2">
+        <f>G114*2.5</f>
+        <v>312.5</v>
+      </c>
       <c r="H109" s="2"/>
     </row>
     <row r="110" spans="1:12">
@@ -4675,7 +4696,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:9">
       <c r="A113" s="2" t="s">
         <v>3</v>
       </c>
@@ -4695,7 +4716,7 @@
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:9">
       <c r="A114" s="2" t="s">
         <v>3</v>
       </c>
@@ -4711,11 +4732,22 @@
       <c r="E114" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="F114" s="2"/>
-      <c r="G114" s="2"/>
-      <c r="H114" s="2"/>
-    </row>
-    <row r="115" spans="1:11">
+      <c r="F114" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="G114" s="23">
+        <f>MIN(C14+C16,C15+C17)</f>
+        <v>125</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="I114">
+        <f>G115/G114</f>
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
       <c r="A115" s="2" t="s">
         <v>251</v>
       </c>
@@ -4732,11 +4764,16 @@
       <c r="E115" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
+      <c r="F115" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="G115" s="23">
+        <f>MAX(C14+C16,C15+C17)</f>
+        <v>135</v>
+      </c>
       <c r="H115" s="2"/>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:9">
       <c r="A116" s="2" t="s">
         <v>251</v>
       </c>
@@ -4757,7 +4794,7 @@
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:9">
       <c r="A117" s="2" t="s">
         <v>251</v>
       </c>
@@ -4774,11 +4811,16 @@
       <c r="E117" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
+      <c r="F117" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="G117" s="2">
+        <f>MIN(C31*C31,(C164+2*C32)^2)</f>
+        <v>8100</v>
+      </c>
       <c r="H117" s="2"/>
     </row>
-    <row r="118" spans="1:11" ht="39">
+    <row r="118" spans="1:9" ht="39">
       <c r="A118" s="2" t="s">
         <v>147</v>
       </c>
@@ -4793,15 +4835,19 @@
       <c r="E118" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-      <c r="H118" s="2"/>
-      <c r="K118">
-        <f>(750-50-50-12.7*4-7*25.4)/13</f>
-        <v>32.415384615384625</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11">
+      <c r="F118" t="s">
+        <v>626</v>
+      </c>
+      <c r="G118">
+        <f>0.75*1.4*8*(G117)*28*7/1000</f>
+        <v>13335.839999999997</v>
+      </c>
+      <c r="H118" s="2">
+        <f>0.75*1.4*8*(2.237*25.4^2)*28*7/1000</f>
+        <v>2376.1222154879997</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
       <c r="A119" s="2" t="s">
         <v>3</v>
       </c>
@@ -4821,7 +4867,7 @@
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:9">
       <c r="A120" s="2" t="s">
         <v>3</v>
       </c>
@@ -4838,10 +4884,13 @@
         <v>263</v>
       </c>
       <c r="F120" s="2"/>
-      <c r="G120" s="2"/>
+      <c r="G120" s="2">
+        <f>C95*(13*G114*SQRT(G117)*SQRT(C10)/1000)*(1+100/(6*G114))</f>
+        <v>6139.4659173253822</v>
+      </c>
       <c r="H120" s="2"/>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:9">
       <c r="A121" s="2" t="s">
         <v>3</v>
       </c>
@@ -4856,14 +4905,17 @@
         <v>266</v>
       </c>
       <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
+      <c r="G121" s="2">
+        <f>G120*0.75</f>
+        <v>4604.5994379940366</v>
+      </c>
       <c r="H121" s="2"/>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:9">
       <c r="A122" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B122" s="13" t="s">
         <v>268</v>
       </c>
       <c r="C122" s="5">
@@ -4880,11 +4932,11 @@
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:9">
       <c r="A123" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B123" s="13" t="s">
         <v>270</v>
       </c>
       <c r="C123" s="5">
@@ -4900,16 +4952,12 @@
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
-      <c r="K123">
-        <f>(C12-2*50-4*9.5-9*25.4)/8</f>
-        <v>41.674999999999997</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11">
+    </row>
+    <row r="124" spans="1:9">
       <c r="A124" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B124" s="13" t="s">
         <v>272</v>
       </c>
       <c r="C124" s="5">
@@ -4926,11 +4974,11 @@
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
     </row>
-    <row r="125" spans="1:11" ht="25">
+    <row r="125" spans="1:9" ht="25">
       <c r="A125" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B125" s="13" t="s">
         <v>274</v>
       </c>
       <c r="C125" s="5">
@@ -4949,11 +4997,11 @@
         <v>276</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:9">
       <c r="A126" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B126" s="13" t="s">
         <v>278</v>
       </c>
       <c r="C126" s="5">
@@ -4970,11 +5018,11 @@
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:9">
       <c r="A127" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="B127" s="13" t="s">
         <v>280</v>
       </c>
       <c r="C127" s="5">
@@ -4991,7 +5039,7 @@
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
     </row>
-    <row r="128" spans="1:11" ht="17.75" customHeight="1">
+    <row r="128" spans="1:9" ht="17.75" customHeight="1">
       <c r="A128" s="19" t="s">
         <v>282</v>
       </c>
@@ -5007,7 +5055,7 @@
       <c r="A129" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="B129" s="13" t="s">
         <v>283</v>
       </c>
       <c r="C129" s="5">
@@ -5028,7 +5076,7 @@
       <c r="A130" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="B130" s="13" t="s">
         <v>285</v>
       </c>
       <c r="C130" s="5">
@@ -5049,7 +5097,7 @@
       <c r="A131" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="B131" s="13" t="s">
         <v>287</v>
       </c>
       <c r="C131" s="5">
@@ -5070,7 +5118,7 @@
       <c r="A132" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B132" s="13" t="s">
         <v>290</v>
       </c>
       <c r="C132" s="5">
@@ -5091,7 +5139,7 @@
       <c r="A133" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="B133" s="13" t="s">
         <v>293</v>
       </c>
       <c r="C133" s="5">
@@ -5112,7 +5160,7 @@
       <c r="A134" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="B134" s="13" t="s">
         <v>295</v>
       </c>
       <c r="C134" s="5">
@@ -5133,7 +5181,7 @@
       <c r="A135" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="B135" s="13" t="s">
         <v>297</v>
       </c>
       <c r="C135" s="5">
@@ -5154,7 +5202,7 @@
       <c r="A136" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="B136" s="13" t="s">
         <v>299</v>
       </c>
       <c r="C136" s="5">
@@ -5175,7 +5223,7 @@
       <c r="A137" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="B137" s="13" t="s">
         <v>301</v>
       </c>
       <c r="C137" s="5">
@@ -5196,7 +5244,7 @@
       <c r="A138" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="B138" s="13" t="s">
         <v>303</v>
       </c>
       <c r="C138" s="5">
@@ -5217,7 +5265,7 @@
       <c r="A139" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="B139" s="13" t="s">
         <v>306</v>
       </c>
       <c r="C139" s="5">
@@ -5238,7 +5286,7 @@
       <c r="A140" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="B140" s="13" t="s">
         <v>308</v>
       </c>
       <c r="C140" s="5">
@@ -5259,7 +5307,7 @@
       <c r="A141" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="B141" s="13" t="s">
         <v>310</v>
       </c>
       <c r="C141" s="5" t="str">
@@ -5278,7 +5326,7 @@
       <c r="A142" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="B142" s="13" t="s">
         <v>313</v>
       </c>
       <c r="C142" s="5" t="str">
@@ -5297,7 +5345,7 @@
       <c r="A143" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B143" s="2" t="s">
+      <c r="B143" s="13" t="s">
         <v>315</v>
       </c>
       <c r="C143" s="5">
@@ -5318,7 +5366,7 @@
       <c r="A144" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="B144" s="13" t="s">
         <v>317</v>
       </c>
       <c r="C144" s="5" t="str">
@@ -5337,7 +5385,7 @@
       <c r="A145" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="B145" s="13" t="s">
         <v>319</v>
       </c>
       <c r="C145" s="5">
@@ -5452,7 +5500,7 @@
       <c r="A151" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="B151" s="13" t="s">
         <v>332</v>
       </c>
       <c r="C151" s="5">
@@ -5473,7 +5521,7 @@
       <c r="A152" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B152" s="2" t="s">
+      <c r="B152" s="13" t="s">
         <v>334</v>
       </c>
       <c r="C152" s="5">
@@ -5516,7 +5564,7 @@
       <c r="A154" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="B154" s="13" t="s">
         <v>339</v>
       </c>
       <c r="C154" s="5" t="str">
@@ -5537,7 +5585,7 @@
       <c r="A155" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B155" s="2" t="s">
+      <c r="B155" s="13" t="s">
         <v>343</v>
       </c>
       <c r="C155" s="5">
@@ -5558,7 +5606,7 @@
       <c r="A156" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B156" s="2" t="s">
+      <c r="B156" s="13" t="s">
         <v>345</v>
       </c>
       <c r="C156" s="5">
@@ -5579,7 +5627,7 @@
       <c r="A157" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B157" s="2" t="s">
+      <c r="B157" s="13" t="s">
         <v>347</v>
       </c>
       <c r="C157" s="5">
@@ -5600,7 +5648,7 @@
       <c r="A158" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B158" s="2" t="s">
+      <c r="B158" s="13" t="s">
         <v>349</v>
       </c>
       <c r="C158" s="5">
@@ -5623,7 +5671,7 @@
       <c r="A159" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B159" s="2" t="s">
+      <c r="B159" s="13" t="s">
         <v>352</v>
       </c>
       <c r="C159" s="5" t="str">
@@ -5642,7 +5690,7 @@
       <c r="A160" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B160" s="2" t="s">
+      <c r="B160" s="13" t="s">
         <v>355</v>
       </c>
       <c r="C160" s="5">
@@ -5663,7 +5711,7 @@
       <c r="A161" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B161" s="2" t="s">
+      <c r="B161" s="13" t="s">
         <v>357</v>
       </c>
       <c r="C161" s="5">
@@ -5684,7 +5732,7 @@
       <c r="A162" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B162" s="2" t="s">
+      <c r="B162" s="13" t="s">
         <v>359</v>
       </c>
       <c r="C162" s="5" t="str">
@@ -5703,7 +5751,7 @@
       <c r="A163" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="B163" s="13" t="s">
         <v>362</v>
       </c>
       <c r="C163" s="5">
@@ -5724,7 +5772,7 @@
       <c r="A164" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B164" s="2" t="s">
+      <c r="B164" s="13" t="s">
         <v>364</v>
       </c>
       <c r="C164" s="5">
@@ -5745,7 +5793,7 @@
       <c r="A165" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B165" s="2" t="s">
+      <c r="B165" s="13" t="s">
         <v>365</v>
       </c>
       <c r="C165" s="5">
@@ -5766,7 +5814,7 @@
       <c r="A166" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B166" s="2" t="s">
+      <c r="B166" s="13" t="s">
         <v>367</v>
       </c>
       <c r="C166" s="5">
@@ -5787,7 +5835,7 @@
       <c r="A167" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B167" s="2" t="s">
+      <c r="B167" s="13" t="s">
         <v>369</v>
       </c>
       <c r="C167" s="5">
@@ -5808,7 +5856,7 @@
       <c r="A168" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B168" s="2" t="s">
+      <c r="B168" s="13" t="s">
         <v>371</v>
       </c>
       <c r="C168" s="5">
@@ -5829,7 +5877,7 @@
       <c r="A169" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B169" s="2" t="s">
+      <c r="B169" s="13" t="s">
         <v>373</v>
       </c>
       <c r="C169" s="5">
@@ -5850,7 +5898,7 @@
       <c r="A170" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B170" s="2" t="s">
+      <c r="B170" s="13" t="s">
         <v>375</v>
       </c>
       <c r="C170" s="5">
@@ -5871,7 +5919,7 @@
       <c r="A171" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B171" s="2" t="s">
+      <c r="B171" s="13" t="s">
         <v>377</v>
       </c>
       <c r="C171" s="5" t="str">
@@ -6159,13 +6207,13 @@
       <formula>ISNUMBER(SEARCH("REVISAR",C1))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation sqref="C30" xr:uid="{F6E6E482-2CFA-40AD-99BC-04E46663BB15}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="8">
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>PERFILES!$B$3:$B$125</xm:f>
